--- a/Input Excel Sheets/Mission Profiles/Mission_Profile_ACDesign.xlsx
+++ b/Input Excel Sheets/Mission Profiles/Mission_Profile_ACDesign.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tyty/Documents/MATLAB/AircraftDesignToolbox-Feb23/MAIN/Input Excel Sheets/Mission Profiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{152DF978-EC7E-CB45-A1C4-BEB61E1B8E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854AECFD-D68F-D448-B342-C41787D4FD43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="1" xr2:uid="{AC12A90C-16A5-0547-A6DB-57534C200D25}"/>
   </bookViews>
   <sheets>
     <sheet name="Templates" sheetId="2" r:id="rId1"/>
-    <sheet name="BuffAir" sheetId="8" r:id="rId2"/>
-    <sheet name="MD80" sheetId="6" r:id="rId3"/>
-    <sheet name="B717" sheetId="4" r:id="rId4"/>
+    <sheet name="Outbound Short (KASE -&gt; KDEN)" sheetId="10" r:id="rId2"/>
+    <sheet name="Inbound Short (KDEN -&gt; KASE)" sheetId="8" r:id="rId3"/>
+    <sheet name="Outbound Long (KASE -&gt; KORD)" sheetId="9" r:id="rId4"/>
+    <sheet name="Inbound Long (KORD -&gt; KASE)" sheetId="11" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="40">
   <si>
     <t>Takeoff</t>
   </si>
@@ -165,7 +166,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -218,15 +219,8 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -251,20 +245,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1"/>
-        <bgColor theme="1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor theme="0" tint="-0.14999847407452621"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="13">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -395,56 +377,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -470,24 +407,66 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="43">
+  <dxfs count="78">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1356,6 +1335,772 @@
         <scheme val="none"/>
       </font>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1370,38 +2115,76 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2D10B45D-8452-AE44-AD9C-5A8977E27B92}" name="Table32323" displayName="Table32323" ref="A1:J160" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28" tableBorderDxfId="27">
-  <autoFilter ref="A1:J160" xr:uid="{2D10B45D-8452-AE44-AD9C-5A8977E27B92}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{DE818DBB-2F5B-F74B-B78B-CA139A754B2D}" name="Table323235" displayName="Table323235" ref="A1:J160" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63" tableBorderDxfId="62">
+  <autoFilter ref="A1:J160" xr:uid="{DE818DBB-2F5B-F74B-B78B-CA139A754B2D}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{0DC1C22F-A822-3E46-8AF2-E11369D1E14E}" name="Segment #" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{7191E28E-8681-294B-8346-8E8922B09DC8}" name="Segment Type" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{5ABAFDAB-EF06-AC43-B41E-B141DE9CE5B1}" name="Input 1" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{2974F4BF-9E70-5944-8F8A-E4481669EFE8}" name="Input 2" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{AF86D66B-B471-3748-9AD4-FB06E11D7F4D}" name="Input 3" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{17610254-944B-3D47-82D1-83A7819F3A69}" name="Input 4" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{DF7C8F88-1C64-2746-8E85-95651DEECAA9}" name="Input 5" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{25A49959-DB36-5B4B-9797-8792C9EC149B}" name="Input 6" dataDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{F20445AA-62A3-BE48-8E7E-D77A45719A6D}" name="Input 7" dataDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{9FDDC896-DE19-0F40-83FA-427FA1A18BA8}" name="Input 8" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{477917ED-3D19-544C-88BC-AD859CA07A6A}" name="Segment #" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{7EEAFF24-6537-E74B-A259-F182AA38EDFA}" name="Segment Type" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{E210CE59-A508-B248-9D51-F92643D3CAA6}" name="Input 1" dataDxfId="59"/>
+    <tableColumn id="4" xr3:uid="{E85DE2C5-4F71-984A-A5A4-3B88980308BB}" name="Input 2" dataDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{99179F65-6EB8-644F-B469-433CD4AE2071}" name="Input 3" dataDxfId="57"/>
+    <tableColumn id="6" xr3:uid="{A3770DD9-4FC0-E04A-8D0B-DAAC8FED19CE}" name="Input 4" dataDxfId="56"/>
+    <tableColumn id="7" xr3:uid="{D9B5143D-6234-1D4C-A011-CD78D3D88F68}" name="Input 5" dataDxfId="55"/>
+    <tableColumn id="8" xr3:uid="{8B714DF7-F599-B748-8B74-7049A1B0082F}" name="Input 6" dataDxfId="54"/>
+    <tableColumn id="9" xr3:uid="{BD0D4A5C-3D61-D947-B1DF-EE657905A624}" name="Input 7" dataDxfId="53"/>
+    <tableColumn id="10" xr3:uid="{97DD83FF-301C-FD4C-9258-6111BCDE4166}" name="Input 8" dataDxfId="52"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{01ACFFE1-E87D-4DC0-A2C1-890D4AFF0045}" name="Table3232" displayName="Table3232" ref="A1:J164" totalsRowShown="0" headerRowDxfId="42" dataDxfId="41" tableBorderDxfId="40">
-  <autoFilter ref="A1:J164" xr:uid="{E9D8E600-FE9F-5C45-8634-0D6DD0E667E3}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2D10B45D-8452-AE44-AD9C-5A8977E27B92}" name="Table32323" displayName="Table32323" ref="A1:J160" totalsRowShown="0" headerRowDxfId="77" dataDxfId="76" tableBorderDxfId="75">
+  <autoFilter ref="A1:J160" xr:uid="{2D10B45D-8452-AE44-AD9C-5A8977E27B92}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{B632CFA7-C8C4-483A-B7C8-BDC67FAF568C}" name="Segment #" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{1D7609CC-04AB-4FC9-A597-EF5F8D1FC695}" name="Segment Type" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{C72631D4-B330-484F-8526-8C2EAF5DCF27}" name="Input 1" dataDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{CE5437A5-B81D-4B09-9A18-306DB1A626F0}" name="Input 2" dataDxfId="36"/>
-    <tableColumn id="5" xr3:uid="{439065A9-5CE9-476C-BAFA-52A281C88B86}" name="Input 3" dataDxfId="35"/>
-    <tableColumn id="6" xr3:uid="{06DCC8E2-B8CF-4844-8A8A-4D4032C87DC3}" name="Input 4" dataDxfId="34"/>
-    <tableColumn id="7" xr3:uid="{743426BA-10A8-4FE4-9575-E4B4F2181BA5}" name="Input 5" dataDxfId="33"/>
-    <tableColumn id="8" xr3:uid="{A946E6CC-7864-4503-A444-8F8A5F5C4575}" name="Input 6" dataDxfId="32"/>
-    <tableColumn id="9" xr3:uid="{E998E880-3942-43FF-A8B6-93782FACC54B}" name="Input 7" dataDxfId="31"/>
-    <tableColumn id="10" xr3:uid="{D2BDBD43-0347-452D-B3DC-B58D4641398E}" name="Input 8" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{0DC1C22F-A822-3E46-8AF2-E11369D1E14E}" name="Segment #" dataDxfId="74"/>
+    <tableColumn id="2" xr3:uid="{7191E28E-8681-294B-8346-8E8922B09DC8}" name="Segment Type" dataDxfId="73"/>
+    <tableColumn id="3" xr3:uid="{5ABAFDAB-EF06-AC43-B41E-B141DE9CE5B1}" name="Input 1" dataDxfId="72"/>
+    <tableColumn id="4" xr3:uid="{2974F4BF-9E70-5944-8F8A-E4481669EFE8}" name="Input 2" dataDxfId="71"/>
+    <tableColumn id="5" xr3:uid="{AF86D66B-B471-3748-9AD4-FB06E11D7F4D}" name="Input 3" dataDxfId="70"/>
+    <tableColumn id="6" xr3:uid="{17610254-944B-3D47-82D1-83A7819F3A69}" name="Input 4" dataDxfId="69"/>
+    <tableColumn id="7" xr3:uid="{DF7C8F88-1C64-2746-8E85-95651DEECAA9}" name="Input 5" dataDxfId="68"/>
+    <tableColumn id="8" xr3:uid="{25A49959-DB36-5B4B-9797-8792C9EC149B}" name="Input 6" dataDxfId="67"/>
+    <tableColumn id="9" xr3:uid="{F20445AA-62A3-BE48-8E7E-D77A45719A6D}" name="Input 7" dataDxfId="66"/>
+    <tableColumn id="10" xr3:uid="{9FDDC896-DE19-0F40-83FA-427FA1A18BA8}" name="Input 8" dataDxfId="65"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{609F90AE-1EEC-FD4B-843C-A0269AE7C24D}" name="Table323236" displayName="Table323236" ref="A1:J160" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50" tableBorderDxfId="49">
+  <autoFilter ref="A1:J160" xr:uid="{609F90AE-1EEC-FD4B-843C-A0269AE7C24D}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{E58A7C4B-F200-EB42-9919-52D0B97ADD5C}" name="Segment #" dataDxfId="48"/>
+    <tableColumn id="2" xr3:uid="{6DDEAFAD-9D2F-CC46-9B88-86E19AA030B0}" name="Segment Type" dataDxfId="47"/>
+    <tableColumn id="3" xr3:uid="{7D9F2DE7-A364-A948-A553-18185CA41CD7}" name="Input 1" dataDxfId="46"/>
+    <tableColumn id="4" xr3:uid="{8289C5DC-9B06-7343-B4A5-DCAA355B0311}" name="Input 2" dataDxfId="45"/>
+    <tableColumn id="5" xr3:uid="{E2E0511E-32AE-DE4F-AD31-E9DE484606E9}" name="Input 3" dataDxfId="44"/>
+    <tableColumn id="6" xr3:uid="{0283C34E-0800-4142-802A-05EFCA4F7E1D}" name="Input 4" dataDxfId="43"/>
+    <tableColumn id="7" xr3:uid="{A0418696-2EA7-8E4A-ADE2-BE35DFB5C9AD}" name="Input 5" dataDxfId="42"/>
+    <tableColumn id="8" xr3:uid="{8585A179-35DE-134C-9510-5AAB28ED8CE0}" name="Input 6" dataDxfId="41"/>
+    <tableColumn id="9" xr3:uid="{2E3D3D9A-BACB-044D-9AC2-962F8C71ECAC}" name="Input 7" dataDxfId="40"/>
+    <tableColumn id="10" xr3:uid="{8217FF77-46AB-CA41-AE50-FD15855435D9}" name="Input 8" dataDxfId="39"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2967264D-CD9F-7D4E-87C6-81F76F006876}" name="Table323237" displayName="Table323237" ref="A1:J160" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37" tableBorderDxfId="36">
+  <autoFilter ref="A1:J160" xr:uid="{2967264D-CD9F-7D4E-87C6-81F76F006876}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{CC4D28DB-5999-7346-94AD-00223790F0DE}" name="Segment #" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{80FF9AB4-1F97-C043-8251-C4C42143FADA}" name="Segment Type" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{6B4DBEBB-5DEA-D64C-9149-B3E3BF80E899}" name="Input 1" dataDxfId="33"/>
+    <tableColumn id="4" xr3:uid="{F2700B14-77E3-D547-8A61-F0F258E2B5A8}" name="Input 2" dataDxfId="32"/>
+    <tableColumn id="5" xr3:uid="{F79021C3-125B-B143-B99A-547B7A56DCEF}" name="Input 3" dataDxfId="31"/>
+    <tableColumn id="6" xr3:uid="{69CB676A-6F4D-624A-A2D2-64760F667420}" name="Input 4" dataDxfId="30"/>
+    <tableColumn id="7" xr3:uid="{1D1259CB-FC6B-A241-ADF9-1D1E7BFDDA48}" name="Input 5" dataDxfId="29"/>
+    <tableColumn id="8" xr3:uid="{53ECE374-5110-3C40-B6E5-70DC8FEDF644}" name="Input 6" dataDxfId="28"/>
+    <tableColumn id="9" xr3:uid="{D3AA5D8B-BA68-524B-80CF-D35E7DE3CFC9}" name="Input 7" dataDxfId="27"/>
+    <tableColumn id="10" xr3:uid="{680EE602-4354-EA43-BEB4-1F8C8F56B32D}" name="Input 8" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2055,21 +2838,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A25:E26">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:F12 F13:F20 B15:E20 A21:F21 B22:F23">
-    <cfRule type="expression" dxfId="15" priority="2">
+    <cfRule type="expression" dxfId="24" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{213DEA30-A76E-BD4D-9236-C8CB76CC5C83}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D010EBB-AB25-434B-845C-43ECD6A9DFE7}">
   <dimension ref="A1:J160"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2176,7 +2960,7 @@
       <c r="C5" s="21">
         <v>7815</v>
       </c>
-      <c r="D5" s="37">
+      <c r="D5" s="25">
         <v>2.56</v>
       </c>
       <c r="E5" s="21">
@@ -2223,13 +3007,13 @@
         <v>7815</v>
       </c>
       <c r="D7" s="21">
-        <v>35000</v>
+        <v>22000</v>
       </c>
       <c r="E7" s="24">
         <v>0.217</v>
       </c>
       <c r="F7" s="24">
-        <v>0.74</v>
+        <v>0.63</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -2266,15 +3050,14 @@
       <c r="A9" s="19"/>
       <c r="B9" s="21"/>
       <c r="C9" s="21">
-        <f>D7</f>
-        <v>35000</v>
+        <v>19000</v>
       </c>
       <c r="D9" s="21">
-        <v>650</v>
+        <v>120</v>
       </c>
       <c r="E9" s="21">
         <f>F7</f>
-        <v>0.74</v>
+        <v>0.63</v>
       </c>
       <c r="F9" s="21">
         <v>0</v>
@@ -4114,37 +4897,36 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="14" priority="5">
+    <cfRule type="expression" dxfId="23" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10:XFD1048576">
-    <cfRule type="expression" dxfId="13" priority="2">
+    <cfRule type="expression" dxfId="22" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1 D1:J1">
-    <cfRule type="expression" dxfId="12" priority="4">
+    <cfRule type="expression" dxfId="21" priority="4">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:XFD9">
-    <cfRule type="expression" dxfId="11" priority="3">
+    <cfRule type="expression" dxfId="19" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:XFD1">
-    <cfRule type="expression" dxfId="10" priority="6">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D5">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="18" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -4152,8 +4934,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2140DA33-D634-412D-A09D-2BFB043838BB}">
-  <dimension ref="A1:J164"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{213DEA30-A76E-BD4D-9236-C8CB76CC5C83}">
+  <dimension ref="A1:J166"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.83203125" style="2" customWidth="1"/>
@@ -4257,10 +5039,10 @@
       <c r="A5" s="19"/>
       <c r="B5" s="21"/>
       <c r="C5" s="21">
-        <v>0</v>
-      </c>
-      <c r="D5" s="21">
-        <v>1.8</v>
+        <v>5433</v>
+      </c>
+      <c r="D5" s="25">
+        <v>2.56</v>
       </c>
       <c r="E5" s="21">
         <v>0.02</v>
@@ -4303,16 +5085,16 @@
       <c r="A7" s="19"/>
       <c r="B7" s="21"/>
       <c r="C7" s="21">
-        <v>0</v>
+        <v>5433</v>
       </c>
       <c r="D7" s="21">
-        <v>30000</v>
+        <v>22000</v>
       </c>
       <c r="E7" s="24">
-        <v>0.21739275999999999</v>
+        <v>0.217</v>
       </c>
       <c r="F7" s="24">
-        <v>0.72</v>
+        <v>0.63</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -4350,14 +5132,14 @@
       <c r="B9" s="21"/>
       <c r="C9" s="21">
         <f>D7</f>
-        <v>30000</v>
+        <v>22000</v>
       </c>
       <c r="D9" s="21">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="E9" s="21">
         <f>F7</f>
-        <v>0.72</v>
+        <v>0.63</v>
       </c>
       <c r="F9" s="21">
         <v>0</v>
@@ -4369,109 +5151,72 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="20">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>32</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="8"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="19"/>
+      <c r="A11" s="21"/>
       <c r="B11" s="21"/>
       <c r="C11" s="21">
-        <v>30000</v>
-      </c>
-      <c r="D11" s="21">
-        <v>35000</v>
-      </c>
-      <c r="E11" s="21">
-        <f>E9</f>
-        <v>0.72</v>
-      </c>
-      <c r="F11" s="21">
-        <v>0.74</v>
-      </c>
-      <c r="G11" s="3">
-        <v>0</v>
-      </c>
+        <v>0.995</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="8"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="20">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>33</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="19"/>
+      <c r="A13" s="21"/>
       <c r="B13" s="21"/>
       <c r="C13" s="21">
-        <f>D11</f>
-        <v>35000</v>
-      </c>
-      <c r="D13" s="21">
-        <v>1000</v>
-      </c>
-      <c r="E13" s="21">
-        <f>F11</f>
-        <v>0.74</v>
-      </c>
-      <c r="F13" s="21">
-        <v>0</v>
-      </c>
+        <v>0.995</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="8"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="20">
-        <v>13</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>16</v>
-      </c>
+      <c r="A14" s="6"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -4481,11 +5226,9 @@
       <c r="J14" s="8"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="21"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21">
-        <v>0.995</v>
-      </c>
+      <c r="A15" s="6"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
@@ -4495,15 +5238,9 @@
       <c r="J15" s="8"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="20">
-        <v>14</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>16</v>
-      </c>
+      <c r="A16" s="6"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -4513,11 +5250,9 @@
       <c r="J16" s="8"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="21"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21">
-        <v>0.995</v>
-      </c>
+      <c r="A17" s="6"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -6231,88 +6966,2133 @@
       <c r="J159" s="8"/>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A160" s="6"/>
-      <c r="B160" s="3"/>
-      <c r="C160" s="3"/>
-      <c r="D160" s="3"/>
-      <c r="E160" s="3"/>
-      <c r="F160" s="3"/>
-      <c r="G160" s="3"/>
-      <c r="H160" s="3"/>
-      <c r="I160" s="3"/>
-      <c r="J160" s="8"/>
-    </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A161" s="6"/>
-      <c r="B161" s="3"/>
-      <c r="C161" s="3"/>
-      <c r="D161" s="3"/>
-      <c r="E161" s="3"/>
-      <c r="F161" s="3"/>
-      <c r="G161" s="3"/>
-      <c r="H161" s="3"/>
-      <c r="I161" s="3"/>
-      <c r="J161" s="8"/>
-    </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A162" s="6"/>
-      <c r="B162" s="3"/>
-      <c r="C162" s="3"/>
-      <c r="D162" s="3"/>
-      <c r="E162" s="3"/>
-      <c r="F162" s="3"/>
-      <c r="G162" s="3"/>
-      <c r="H162" s="3"/>
-      <c r="I162" s="3"/>
-      <c r="J162" s="8"/>
-    </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A163" s="6"/>
-      <c r="B163" s="3"/>
-      <c r="C163" s="3"/>
-      <c r="D163" s="3"/>
-      <c r="E163" s="3"/>
-      <c r="F163" s="3"/>
-      <c r="G163" s="3"/>
-      <c r="H163" s="3"/>
-      <c r="I163" s="3"/>
-      <c r="J163" s="8"/>
-    </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A164" s="9"/>
-      <c r="B164" s="10"/>
-      <c r="C164" s="10"/>
-      <c r="D164" s="10"/>
-      <c r="E164" s="10"/>
-      <c r="F164" s="10"/>
-      <c r="G164" s="10"/>
-      <c r="H164" s="10"/>
-      <c r="I164" s="10"/>
-      <c r="J164" s="11"/>
-    </row>
+      <c r="A160" s="9"/>
+      <c r="B160" s="10"/>
+      <c r="C160" s="10"/>
+      <c r="D160" s="10"/>
+      <c r="E160" s="10"/>
+      <c r="F160" s="10"/>
+      <c r="G160" s="10"/>
+      <c r="H160" s="10"/>
+      <c r="I160" s="10"/>
+      <c r="J160" s="11"/>
+    </row>
+    <row r="161" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="162" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="163" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="164" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="165" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="166" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="9" priority="9">
+    <cfRule type="expression" dxfId="17" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A14:XFD1048576">
+  <conditionalFormatting sqref="A10:XFD1048576">
+    <cfRule type="expression" dxfId="16" priority="2">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1 D1:J1">
+    <cfRule type="expression" dxfId="15" priority="4">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5">
+    <cfRule type="expression" dxfId="14" priority="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:XFD9">
+    <cfRule type="expression" dxfId="13" priority="3">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K1:XFD1">
+    <cfRule type="expression" dxfId="12" priority="6">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AB4AE65-6805-654B-822E-6794F8A95DDE}">
+  <dimension ref="A1:J160"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.83203125" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="10.83203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="19" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="18">
+        <v>1</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="7"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="19"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21">
+        <v>0.995</v>
+      </c>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="20">
+        <v>2</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="8"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="19"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21">
+        <v>7815</v>
+      </c>
+      <c r="D5" s="25">
+        <v>2.56</v>
+      </c>
+      <c r="E5" s="21">
+        <v>0.02</v>
+      </c>
+      <c r="F5">
+        <v>0.05</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="20">
+        <v>3</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="8"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="19"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21">
+        <v>7815</v>
+      </c>
+      <c r="D7" s="21">
+        <v>33000</v>
+      </c>
+      <c r="E7" s="24">
+        <v>0.217</v>
+      </c>
+      <c r="F7" s="24">
+        <v>0.63</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="20">
+        <v>4</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="19"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21">
+        <f>D7</f>
+        <v>33000</v>
+      </c>
+      <c r="D9" s="21">
+        <v>800</v>
+      </c>
+      <c r="E9" s="21">
+        <v>0.76</v>
+      </c>
+      <c r="F9" s="21">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="20">
+        <v>13</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="8"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="21"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21">
+        <v>0.995</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="8"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="20">
+        <v>14</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="21"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21">
+        <v>0.995</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="8"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="6"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="8"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="6"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="8"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="6"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="8"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="8"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="6"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="8"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="6"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="8"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="6"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="8"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="6"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="8"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="6"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="8"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="6"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="8"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="6"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="8"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="6"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="8"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="6"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="8"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="6"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="8"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="6"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="8"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="6"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="8"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="6"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="8"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="6"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="8"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="8"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="6"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="8"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="6"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="8"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="6"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="8"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="6"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="8"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="6"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="8"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="6"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="8"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="6"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="8"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="6"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="8"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="6"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="8"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="6"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="8"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="6"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="8"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="6"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="8"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="6"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="8"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="6"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="8"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="6"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="8"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="6"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="8"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="6"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="8"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="6"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="8"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="6"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="3"/>
+      <c r="J51" s="8"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="6"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3"/>
+      <c r="I52" s="3"/>
+      <c r="J52" s="8"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="6"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="8"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="6"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
+      <c r="J54" s="8"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="6"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="3"/>
+      <c r="J55" s="8"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="6"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
+      <c r="J56" s="8"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="6"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="3"/>
+      <c r="J57" s="8"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="6"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="H58" s="3"/>
+      <c r="I58" s="3"/>
+      <c r="J58" s="8"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="6"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+      <c r="I59" s="3"/>
+      <c r="J59" s="8"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="6"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
+      <c r="I60" s="3"/>
+      <c r="J60" s="8"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="6"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3"/>
+      <c r="I61" s="3"/>
+      <c r="J61" s="8"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="6"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="3"/>
+      <c r="J62" s="8"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="6"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
+      <c r="H63" s="3"/>
+      <c r="I63" s="3"/>
+      <c r="J63" s="8"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="6"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
+      <c r="H64" s="3"/>
+      <c r="I64" s="3"/>
+      <c r="J64" s="8"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" s="6"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3"/>
+      <c r="H65" s="3"/>
+      <c r="I65" s="3"/>
+      <c r="J65" s="8"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="6"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
+      <c r="H66" s="3"/>
+      <c r="I66" s="3"/>
+      <c r="J66" s="8"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" s="6"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="H67" s="3"/>
+      <c r="I67" s="3"/>
+      <c r="J67" s="8"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" s="6"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="H68" s="3"/>
+      <c r="I68" s="3"/>
+      <c r="J68" s="8"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" s="6"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3"/>
+      <c r="J69" s="8"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" s="6"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="3"/>
+      <c r="J70" s="8"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" s="6"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
+      <c r="H71" s="3"/>
+      <c r="I71" s="3"/>
+      <c r="J71" s="8"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="6"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="3"/>
+      <c r="I72" s="3"/>
+      <c r="J72" s="8"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" s="6"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
+      <c r="H73" s="3"/>
+      <c r="I73" s="3"/>
+      <c r="J73" s="8"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" s="6"/>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="3"/>
+      <c r="J74" s="8"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" s="6"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
+      <c r="H75" s="3"/>
+      <c r="I75" s="3"/>
+      <c r="J75" s="8"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" s="6"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="3"/>
+      <c r="J76" s="8"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" s="6"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3"/>
+      <c r="I77" s="3"/>
+      <c r="J77" s="8"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" s="6"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3"/>
+      <c r="I78" s="3"/>
+      <c r="J78" s="8"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" s="6"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3"/>
+      <c r="H79" s="3"/>
+      <c r="I79" s="3"/>
+      <c r="J79" s="8"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" s="6"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
+      <c r="H80" s="3"/>
+      <c r="I80" s="3"/>
+      <c r="J80" s="8"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" s="6"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3"/>
+      <c r="H81" s="3"/>
+      <c r="I81" s="3"/>
+      <c r="J81" s="8"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" s="6"/>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
+      <c r="H82" s="3"/>
+      <c r="I82" s="3"/>
+      <c r="J82" s="8"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" s="6"/>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3"/>
+      <c r="H83" s="3"/>
+      <c r="I83" s="3"/>
+      <c r="J83" s="8"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" s="6"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
+      <c r="H84" s="3"/>
+      <c r="I84" s="3"/>
+      <c r="J84" s="8"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" s="6"/>
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3"/>
+      <c r="H85" s="3"/>
+      <c r="I85" s="3"/>
+      <c r="J85" s="8"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" s="6"/>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
+      <c r="H86" s="3"/>
+      <c r="I86" s="3"/>
+      <c r="J86" s="8"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" s="6"/>
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
+      <c r="H87" s="3"/>
+      <c r="I87" s="3"/>
+      <c r="J87" s="8"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" s="6"/>
+      <c r="B88" s="3"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
+      <c r="H88" s="3"/>
+      <c r="I88" s="3"/>
+      <c r="J88" s="8"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" s="6"/>
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
+      <c r="H89" s="3"/>
+      <c r="I89" s="3"/>
+      <c r="J89" s="8"/>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90" s="6"/>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+      <c r="H90" s="3"/>
+      <c r="I90" s="3"/>
+      <c r="J90" s="8"/>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91" s="6"/>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
+      <c r="H91" s="3"/>
+      <c r="I91" s="3"/>
+      <c r="J91" s="8"/>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92" s="6"/>
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
+      <c r="H92" s="3"/>
+      <c r="I92" s="3"/>
+      <c r="J92" s="8"/>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93" s="6"/>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
+      <c r="H93" s="3"/>
+      <c r="I93" s="3"/>
+      <c r="J93" s="8"/>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94" s="6"/>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
+      <c r="H94" s="3"/>
+      <c r="I94" s="3"/>
+      <c r="J94" s="8"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" s="6"/>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
+      <c r="H95" s="3"/>
+      <c r="I95" s="3"/>
+      <c r="J95" s="8"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" s="6"/>
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
+      <c r="H96" s="3"/>
+      <c r="I96" s="3"/>
+      <c r="J96" s="8"/>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97" s="6"/>
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
+      <c r="H97" s="3"/>
+      <c r="I97" s="3"/>
+      <c r="J97" s="8"/>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" s="6"/>
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+      <c r="H98" s="3"/>
+      <c r="I98" s="3"/>
+      <c r="J98" s="8"/>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" s="6"/>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
+      <c r="H99" s="3"/>
+      <c r="I99" s="3"/>
+      <c r="J99" s="8"/>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100" s="6"/>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
+      <c r="H100" s="3"/>
+      <c r="I100" s="3"/>
+      <c r="J100" s="8"/>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A101" s="6"/>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3"/>
+      <c r="H101" s="3"/>
+      <c r="I101" s="3"/>
+      <c r="J101" s="8"/>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102" s="6"/>
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3"/>
+      <c r="H102" s="3"/>
+      <c r="I102" s="3"/>
+      <c r="J102" s="8"/>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A103" s="6"/>
+      <c r="B103" s="3"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="3"/>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3"/>
+      <c r="H103" s="3"/>
+      <c r="I103" s="3"/>
+      <c r="J103" s="8"/>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" s="6"/>
+      <c r="B104" s="3"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="3"/>
+      <c r="F104" s="3"/>
+      <c r="G104" s="3"/>
+      <c r="H104" s="3"/>
+      <c r="I104" s="3"/>
+      <c r="J104" s="8"/>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105" s="6"/>
+      <c r="B105" s="3"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="3"/>
+      <c r="F105" s="3"/>
+      <c r="G105" s="3"/>
+      <c r="H105" s="3"/>
+      <c r="I105" s="3"/>
+      <c r="J105" s="8"/>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106" s="6"/>
+      <c r="B106" s="3"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3"/>
+      <c r="H106" s="3"/>
+      <c r="I106" s="3"/>
+      <c r="J106" s="8"/>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A107" s="6"/>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3"/>
+      <c r="H107" s="3"/>
+      <c r="I107" s="3"/>
+      <c r="J107" s="8"/>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" s="6"/>
+      <c r="B108" s="3"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="3"/>
+      <c r="F108" s="3"/>
+      <c r="G108" s="3"/>
+      <c r="H108" s="3"/>
+      <c r="I108" s="3"/>
+      <c r="J108" s="8"/>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A109" s="6"/>
+      <c r="B109" s="3"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="3"/>
+      <c r="F109" s="3"/>
+      <c r="G109" s="3"/>
+      <c r="H109" s="3"/>
+      <c r="I109" s="3"/>
+      <c r="J109" s="8"/>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A110" s="6"/>
+      <c r="B110" s="3"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3"/>
+      <c r="H110" s="3"/>
+      <c r="I110" s="3"/>
+      <c r="J110" s="8"/>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A111" s="6"/>
+      <c r="B111" s="3"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="3"/>
+      <c r="F111" s="3"/>
+      <c r="G111" s="3"/>
+      <c r="H111" s="3"/>
+      <c r="I111" s="3"/>
+      <c r="J111" s="8"/>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A112" s="6"/>
+      <c r="B112" s="3"/>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3"/>
+      <c r="E112" s="3"/>
+      <c r="F112" s="3"/>
+      <c r="G112" s="3"/>
+      <c r="H112" s="3"/>
+      <c r="I112" s="3"/>
+      <c r="J112" s="8"/>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A113" s="6"/>
+      <c r="B113" s="3"/>
+      <c r="C113" s="3"/>
+      <c r="D113" s="3"/>
+      <c r="E113" s="3"/>
+      <c r="F113" s="3"/>
+      <c r="G113" s="3"/>
+      <c r="H113" s="3"/>
+      <c r="I113" s="3"/>
+      <c r="J113" s="8"/>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A114" s="6"/>
+      <c r="B114" s="3"/>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="3"/>
+      <c r="F114" s="3"/>
+      <c r="G114" s="3"/>
+      <c r="H114" s="3"/>
+      <c r="I114" s="3"/>
+      <c r="J114" s="8"/>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A115" s="6"/>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="3"/>
+      <c r="F115" s="3"/>
+      <c r="G115" s="3"/>
+      <c r="H115" s="3"/>
+      <c r="I115" s="3"/>
+      <c r="J115" s="8"/>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A116" s="6"/>
+      <c r="B116" s="3"/>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="3"/>
+      <c r="F116" s="3"/>
+      <c r="G116" s="3"/>
+      <c r="H116" s="3"/>
+      <c r="I116" s="3"/>
+      <c r="J116" s="8"/>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A117" s="6"/>
+      <c r="B117" s="3"/>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3"/>
+      <c r="E117" s="3"/>
+      <c r="F117" s="3"/>
+      <c r="G117" s="3"/>
+      <c r="H117" s="3"/>
+      <c r="I117" s="3"/>
+      <c r="J117" s="8"/>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A118" s="6"/>
+      <c r="B118" s="3"/>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="3"/>
+      <c r="F118" s="3"/>
+      <c r="G118" s="3"/>
+      <c r="H118" s="3"/>
+      <c r="I118" s="3"/>
+      <c r="J118" s="8"/>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A119" s="6"/>
+      <c r="B119" s="3"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
+      <c r="E119" s="3"/>
+      <c r="F119" s="3"/>
+      <c r="G119" s="3"/>
+      <c r="H119" s="3"/>
+      <c r="I119" s="3"/>
+      <c r="J119" s="8"/>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A120" s="6"/>
+      <c r="B120" s="3"/>
+      <c r="C120" s="3"/>
+      <c r="D120" s="3"/>
+      <c r="E120" s="3"/>
+      <c r="F120" s="3"/>
+      <c r="G120" s="3"/>
+      <c r="H120" s="3"/>
+      <c r="I120" s="3"/>
+      <c r="J120" s="8"/>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A121" s="6"/>
+      <c r="B121" s="3"/>
+      <c r="C121" s="3"/>
+      <c r="D121" s="3"/>
+      <c r="E121" s="3"/>
+      <c r="F121" s="3"/>
+      <c r="G121" s="3"/>
+      <c r="H121" s="3"/>
+      <c r="I121" s="3"/>
+      <c r="J121" s="8"/>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A122" s="6"/>
+      <c r="B122" s="3"/>
+      <c r="C122" s="3"/>
+      <c r="D122" s="3"/>
+      <c r="E122" s="3"/>
+      <c r="F122" s="3"/>
+      <c r="G122" s="3"/>
+      <c r="H122" s="3"/>
+      <c r="I122" s="3"/>
+      <c r="J122" s="8"/>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A123" s="6"/>
+      <c r="B123" s="3"/>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3"/>
+      <c r="E123" s="3"/>
+      <c r="F123" s="3"/>
+      <c r="G123" s="3"/>
+      <c r="H123" s="3"/>
+      <c r="I123" s="3"/>
+      <c r="J123" s="8"/>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A124" s="6"/>
+      <c r="B124" s="3"/>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3"/>
+      <c r="E124" s="3"/>
+      <c r="F124" s="3"/>
+      <c r="G124" s="3"/>
+      <c r="H124" s="3"/>
+      <c r="I124" s="3"/>
+      <c r="J124" s="8"/>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A125" s="6"/>
+      <c r="B125" s="3"/>
+      <c r="C125" s="3"/>
+      <c r="D125" s="3"/>
+      <c r="E125" s="3"/>
+      <c r="F125" s="3"/>
+      <c r="G125" s="3"/>
+      <c r="H125" s="3"/>
+      <c r="I125" s="3"/>
+      <c r="J125" s="8"/>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A126" s="6"/>
+      <c r="B126" s="3"/>
+      <c r="C126" s="3"/>
+      <c r="D126" s="3"/>
+      <c r="E126" s="3"/>
+      <c r="F126" s="3"/>
+      <c r="G126" s="3"/>
+      <c r="H126" s="3"/>
+      <c r="I126" s="3"/>
+      <c r="J126" s="8"/>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A127" s="6"/>
+      <c r="B127" s="3"/>
+      <c r="C127" s="3"/>
+      <c r="D127" s="3"/>
+      <c r="E127" s="3"/>
+      <c r="F127" s="3"/>
+      <c r="G127" s="3"/>
+      <c r="H127" s="3"/>
+      <c r="I127" s="3"/>
+      <c r="J127" s="8"/>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A128" s="6"/>
+      <c r="B128" s="3"/>
+      <c r="C128" s="3"/>
+      <c r="D128" s="3"/>
+      <c r="E128" s="3"/>
+      <c r="F128" s="3"/>
+      <c r="G128" s="3"/>
+      <c r="H128" s="3"/>
+      <c r="I128" s="3"/>
+      <c r="J128" s="8"/>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A129" s="6"/>
+      <c r="B129" s="3"/>
+      <c r="C129" s="3"/>
+      <c r="D129" s="3"/>
+      <c r="E129" s="3"/>
+      <c r="F129" s="3"/>
+      <c r="G129" s="3"/>
+      <c r="H129" s="3"/>
+      <c r="I129" s="3"/>
+      <c r="J129" s="8"/>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A130" s="6"/>
+      <c r="B130" s="3"/>
+      <c r="C130" s="3"/>
+      <c r="D130" s="3"/>
+      <c r="E130" s="3"/>
+      <c r="F130" s="3"/>
+      <c r="G130" s="3"/>
+      <c r="H130" s="3"/>
+      <c r="I130" s="3"/>
+      <c r="J130" s="8"/>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A131" s="6"/>
+      <c r="B131" s="3"/>
+      <c r="C131" s="3"/>
+      <c r="D131" s="3"/>
+      <c r="E131" s="3"/>
+      <c r="F131" s="3"/>
+      <c r="G131" s="3"/>
+      <c r="H131" s="3"/>
+      <c r="I131" s="3"/>
+      <c r="J131" s="8"/>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A132" s="6"/>
+      <c r="B132" s="3"/>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3"/>
+      <c r="E132" s="3"/>
+      <c r="F132" s="3"/>
+      <c r="G132" s="3"/>
+      <c r="H132" s="3"/>
+      <c r="I132" s="3"/>
+      <c r="J132" s="8"/>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A133" s="6"/>
+      <c r="B133" s="3"/>
+      <c r="C133" s="3"/>
+      <c r="D133" s="3"/>
+      <c r="E133" s="3"/>
+      <c r="F133" s="3"/>
+      <c r="G133" s="3"/>
+      <c r="H133" s="3"/>
+      <c r="I133" s="3"/>
+      <c r="J133" s="8"/>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A134" s="6"/>
+      <c r="B134" s="3"/>
+      <c r="C134" s="3"/>
+      <c r="D134" s="3"/>
+      <c r="E134" s="3"/>
+      <c r="F134" s="3"/>
+      <c r="G134" s="3"/>
+      <c r="H134" s="3"/>
+      <c r="I134" s="3"/>
+      <c r="J134" s="8"/>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A135" s="6"/>
+      <c r="B135" s="3"/>
+      <c r="C135" s="3"/>
+      <c r="D135" s="3"/>
+      <c r="E135" s="3"/>
+      <c r="F135" s="3"/>
+      <c r="G135" s="3"/>
+      <c r="H135" s="3"/>
+      <c r="I135" s="3"/>
+      <c r="J135" s="8"/>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A136" s="6"/>
+      <c r="B136" s="3"/>
+      <c r="C136" s="3"/>
+      <c r="D136" s="3"/>
+      <c r="E136" s="3"/>
+      <c r="F136" s="3"/>
+      <c r="G136" s="3"/>
+      <c r="H136" s="3"/>
+      <c r="I136" s="3"/>
+      <c r="J136" s="8"/>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A137" s="6"/>
+      <c r="B137" s="3"/>
+      <c r="C137" s="3"/>
+      <c r="D137" s="3"/>
+      <c r="E137" s="3"/>
+      <c r="F137" s="3"/>
+      <c r="G137" s="3"/>
+      <c r="H137" s="3"/>
+      <c r="I137" s="3"/>
+      <c r="J137" s="8"/>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A138" s="6"/>
+      <c r="B138" s="3"/>
+      <c r="C138" s="3"/>
+      <c r="D138" s="3"/>
+      <c r="E138" s="3"/>
+      <c r="F138" s="3"/>
+      <c r="G138" s="3"/>
+      <c r="H138" s="3"/>
+      <c r="I138" s="3"/>
+      <c r="J138" s="8"/>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A139" s="6"/>
+      <c r="B139" s="3"/>
+      <c r="C139" s="3"/>
+      <c r="D139" s="3"/>
+      <c r="E139" s="3"/>
+      <c r="F139" s="3"/>
+      <c r="G139" s="3"/>
+      <c r="H139" s="3"/>
+      <c r="I139" s="3"/>
+      <c r="J139" s="8"/>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A140" s="6"/>
+      <c r="B140" s="3"/>
+      <c r="C140" s="3"/>
+      <c r="D140" s="3"/>
+      <c r="E140" s="3"/>
+      <c r="F140" s="3"/>
+      <c r="G140" s="3"/>
+      <c r="H140" s="3"/>
+      <c r="I140" s="3"/>
+      <c r="J140" s="8"/>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A141" s="6"/>
+      <c r="B141" s="3"/>
+      <c r="C141" s="3"/>
+      <c r="D141" s="3"/>
+      <c r="E141" s="3"/>
+      <c r="F141" s="3"/>
+      <c r="G141" s="3"/>
+      <c r="H141" s="3"/>
+      <c r="I141" s="3"/>
+      <c r="J141" s="8"/>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A142" s="6"/>
+      <c r="B142" s="3"/>
+      <c r="C142" s="3"/>
+      <c r="D142" s="3"/>
+      <c r="E142" s="3"/>
+      <c r="F142" s="3"/>
+      <c r="G142" s="3"/>
+      <c r="H142" s="3"/>
+      <c r="I142" s="3"/>
+      <c r="J142" s="8"/>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A143" s="6"/>
+      <c r="B143" s="3"/>
+      <c r="C143" s="3"/>
+      <c r="D143" s="3"/>
+      <c r="E143" s="3"/>
+      <c r="F143" s="3"/>
+      <c r="G143" s="3"/>
+      <c r="H143" s="3"/>
+      <c r="I143" s="3"/>
+      <c r="J143" s="8"/>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A144" s="6"/>
+      <c r="B144" s="3"/>
+      <c r="C144" s="3"/>
+      <c r="D144" s="3"/>
+      <c r="E144" s="3"/>
+      <c r="F144" s="3"/>
+      <c r="G144" s="3"/>
+      <c r="H144" s="3"/>
+      <c r="I144" s="3"/>
+      <c r="J144" s="8"/>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A145" s="6"/>
+      <c r="B145" s="3"/>
+      <c r="C145" s="3"/>
+      <c r="D145" s="3"/>
+      <c r="E145" s="3"/>
+      <c r="F145" s="3"/>
+      <c r="G145" s="3"/>
+      <c r="H145" s="3"/>
+      <c r="I145" s="3"/>
+      <c r="J145" s="8"/>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A146" s="6"/>
+      <c r="B146" s="3"/>
+      <c r="C146" s="3"/>
+      <c r="D146" s="3"/>
+      <c r="E146" s="3"/>
+      <c r="F146" s="3"/>
+      <c r="G146" s="3"/>
+      <c r="H146" s="3"/>
+      <c r="I146" s="3"/>
+      <c r="J146" s="8"/>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A147" s="6"/>
+      <c r="B147" s="3"/>
+      <c r="C147" s="3"/>
+      <c r="D147" s="3"/>
+      <c r="E147" s="3"/>
+      <c r="F147" s="3"/>
+      <c r="G147" s="3"/>
+      <c r="H147" s="3"/>
+      <c r="I147" s="3"/>
+      <c r="J147" s="8"/>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A148" s="6"/>
+      <c r="B148" s="3"/>
+      <c r="C148" s="3"/>
+      <c r="D148" s="3"/>
+      <c r="E148" s="3"/>
+      <c r="F148" s="3"/>
+      <c r="G148" s="3"/>
+      <c r="H148" s="3"/>
+      <c r="I148" s="3"/>
+      <c r="J148" s="8"/>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A149" s="6"/>
+      <c r="B149" s="3"/>
+      <c r="C149" s="3"/>
+      <c r="D149" s="3"/>
+      <c r="E149" s="3"/>
+      <c r="F149" s="3"/>
+      <c r="G149" s="3"/>
+      <c r="H149" s="3"/>
+      <c r="I149" s="3"/>
+      <c r="J149" s="8"/>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A150" s="6"/>
+      <c r="B150" s="3"/>
+      <c r="C150" s="3"/>
+      <c r="D150" s="3"/>
+      <c r="E150" s="3"/>
+      <c r="F150" s="3"/>
+      <c r="G150" s="3"/>
+      <c r="H150" s="3"/>
+      <c r="I150" s="3"/>
+      <c r="J150" s="8"/>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A151" s="6"/>
+      <c r="B151" s="3"/>
+      <c r="C151" s="3"/>
+      <c r="D151" s="3"/>
+      <c r="E151" s="3"/>
+      <c r="F151" s="3"/>
+      <c r="G151" s="3"/>
+      <c r="H151" s="3"/>
+      <c r="I151" s="3"/>
+      <c r="J151" s="8"/>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A152" s="6"/>
+      <c r="B152" s="3"/>
+      <c r="C152" s="3"/>
+      <c r="D152" s="3"/>
+      <c r="E152" s="3"/>
+      <c r="F152" s="3"/>
+      <c r="G152" s="3"/>
+      <c r="H152" s="3"/>
+      <c r="I152" s="3"/>
+      <c r="J152" s="8"/>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A153" s="6"/>
+      <c r="B153" s="3"/>
+      <c r="C153" s="3"/>
+      <c r="D153" s="3"/>
+      <c r="E153" s="3"/>
+      <c r="F153" s="3"/>
+      <c r="G153" s="3"/>
+      <c r="H153" s="3"/>
+      <c r="I153" s="3"/>
+      <c r="J153" s="8"/>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A154" s="6"/>
+      <c r="B154" s="3"/>
+      <c r="C154" s="3"/>
+      <c r="D154" s="3"/>
+      <c r="E154" s="3"/>
+      <c r="F154" s="3"/>
+      <c r="G154" s="3"/>
+      <c r="H154" s="3"/>
+      <c r="I154" s="3"/>
+      <c r="J154" s="8"/>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A155" s="6"/>
+      <c r="B155" s="3"/>
+      <c r="C155" s="3"/>
+      <c r="D155" s="3"/>
+      <c r="E155" s="3"/>
+      <c r="F155" s="3"/>
+      <c r="G155" s="3"/>
+      <c r="H155" s="3"/>
+      <c r="I155" s="3"/>
+      <c r="J155" s="8"/>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A156" s="6"/>
+      <c r="B156" s="3"/>
+      <c r="C156" s="3"/>
+      <c r="D156" s="3"/>
+      <c r="E156" s="3"/>
+      <c r="F156" s="3"/>
+      <c r="G156" s="3"/>
+      <c r="H156" s="3"/>
+      <c r="I156" s="3"/>
+      <c r="J156" s="8"/>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A157" s="6"/>
+      <c r="B157" s="3"/>
+      <c r="C157" s="3"/>
+      <c r="D157" s="3"/>
+      <c r="E157" s="3"/>
+      <c r="F157" s="3"/>
+      <c r="G157" s="3"/>
+      <c r="H157" s="3"/>
+      <c r="I157" s="3"/>
+      <c r="J157" s="8"/>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A158" s="6"/>
+      <c r="B158" s="3"/>
+      <c r="C158" s="3"/>
+      <c r="D158" s="3"/>
+      <c r="E158" s="3"/>
+      <c r="F158" s="3"/>
+      <c r="G158" s="3"/>
+      <c r="H158" s="3"/>
+      <c r="I158" s="3"/>
+      <c r="J158" s="8"/>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A159" s="6"/>
+      <c r="B159" s="3"/>
+      <c r="C159" s="3"/>
+      <c r="D159" s="3"/>
+      <c r="E159" s="3"/>
+      <c r="F159" s="3"/>
+      <c r="G159" s="3"/>
+      <c r="H159" s="3"/>
+      <c r="I159" s="3"/>
+      <c r="J159" s="8"/>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A160" s="9"/>
+      <c r="B160" s="10"/>
+      <c r="C160" s="10"/>
+      <c r="D160" s="10"/>
+      <c r="E160" s="10"/>
+      <c r="F160" s="10"/>
+      <c r="G160" s="10"/>
+      <c r="H160" s="10"/>
+      <c r="I160" s="10"/>
+      <c r="J160" s="11"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1">
+    <cfRule type="expression" dxfId="11" priority="5">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A10:XFD1048576">
+    <cfRule type="expression" dxfId="10" priority="2">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1 D1:J1">
+    <cfRule type="expression" dxfId="9" priority="4">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5">
     <cfRule type="expression" dxfId="8" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1 D1:J1">
-    <cfRule type="expression" dxfId="7" priority="8">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:XFD13">
-    <cfRule type="expression" dxfId="6" priority="3">
+  <conditionalFormatting sqref="G2:XFD9">
+    <cfRule type="expression" dxfId="7" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:XFD1">
-    <cfRule type="expression" dxfId="5" priority="10">
+    <cfRule type="expression" dxfId="6" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6323,169 +9103,168 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D337AD70-AEDB-49E7-812A-3DF280E6A32E}">
-  <dimension ref="A1:J182"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A119F18C-D7F6-5E4D-ADD0-ED755A681F08}">
+  <dimension ref="A1:J166"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.83203125" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="19" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="I1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A2" s="26">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="29"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A3" s="30"/>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31">
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="7"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="19"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21">
         <v>0.995</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="27">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="20">
         <v>2</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="27" t="s">
+      <c r="F4" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="32"/>
-    </row>
-    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A5" s="30"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31">
-        <v>0</v>
-      </c>
-      <c r="D5" s="31">
-        <v>2</v>
-      </c>
-      <c r="E5" s="31">
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="8"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="19"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21">
+        <v>5594</v>
+      </c>
+      <c r="D5" s="25">
+        <v>2.56</v>
+      </c>
+      <c r="E5" s="21">
         <v>0.02</v>
       </c>
-      <c r="F5" s="31">
-        <v>6.0000000000000001E-3</v>
+      <c r="F5">
+        <v>0.05</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="8"/>
     </row>
-    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="27">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="20">
         <v>3</v>
       </c>
-      <c r="B6" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="27" t="s">
+      <c r="B6" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="F6" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="32"/>
-    </row>
-    <row r="7" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A7" s="30"/>
-      <c r="B7" s="31"/>
-      <c r="C7" s="31">
-        <v>0</v>
-      </c>
-      <c r="D7" s="31">
-        <v>5000</v>
-      </c>
-      <c r="E7" s="31">
-        <v>0.1</v>
-      </c>
-      <c r="F7" s="31">
-        <v>0.25</v>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="8"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="19"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21">
+        <v>5594</v>
+      </c>
+      <c r="D7" s="21">
+        <v>33000</v>
+      </c>
+      <c r="E7" s="24">
+        <v>0.217</v>
+      </c>
+      <c r="F7" s="24">
+        <v>0.63</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -6494,218 +9273,155 @@
       <c r="I7" s="3"/>
       <c r="J7" s="8"/>
     </row>
-    <row r="8" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A8" s="27">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="20">
         <v>4</v>
       </c>
-      <c r="B8" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="32"/>
-    </row>
-    <row r="9" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A9" s="30"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31">
-        <v>5000</v>
-      </c>
-      <c r="D9" s="31">
-        <v>15000</v>
-      </c>
-      <c r="E9" s="31">
-        <v>0.25</v>
-      </c>
-      <c r="F9" s="31">
-        <v>0.54</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="B8" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="19"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21">
+        <f>D7</f>
+        <v>33000</v>
+      </c>
+      <c r="D9" s="21">
+        <v>800</v>
+      </c>
+      <c r="E9" s="21">
+        <v>0.76</v>
+      </c>
+      <c r="F9" s="21">
         <v>0</v>
       </c>
+      <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="8"/>
     </row>
-    <row r="10" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A10" s="27">
-        <v>5</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="32"/>
-    </row>
-    <row r="11" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A11" s="30"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31">
-        <v>15000</v>
-      </c>
-      <c r="D11" s="31">
-        <v>27000</v>
-      </c>
-      <c r="E11" s="31">
-        <v>0.54</v>
-      </c>
-      <c r="F11" s="31">
-        <v>0.61</v>
-      </c>
-      <c r="G11" s="3">
-        <v>0</v>
-      </c>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="20">
+        <v>13</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="8"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="21"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21">
+        <v>0.995</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="8"/>
     </row>
-    <row r="12" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A12" s="27">
-        <v>5</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="32"/>
-    </row>
-    <row r="13" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A13" s="30"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="31">
-        <v>27000</v>
-      </c>
-      <c r="D13" s="31">
-        <v>37000</v>
-      </c>
-      <c r="E13" s="31">
-        <v>0.61</v>
-      </c>
-      <c r="F13" s="31">
-        <v>0.71</v>
-      </c>
-      <c r="G13" s="3">
-        <v>0</v>
-      </c>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="20">
+        <v>14</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="21"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21">
+        <v>0.995</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="8"/>
     </row>
-    <row r="14" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A14" s="33">
-        <v>6</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="32"/>
-    </row>
-    <row r="15" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="6"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="8"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="35">
-        <v>37000</v>
-      </c>
-      <c r="D15" s="35">
-        <v>2000</v>
-      </c>
-      <c r="E15" s="35">
-        <v>0.71</v>
-      </c>
-      <c r="F15" s="35">
-        <v>0</v>
-      </c>
-      <c r="G15" s="35"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="8"/>
     </row>
-    <row r="16" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A16" s="27">
-        <v>7</v>
-      </c>
-      <c r="B16" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="32"/>
-    </row>
-    <row r="17" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A17" s="31"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="31">
-        <v>0.99</v>
-      </c>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="6"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="8"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -6714,30 +9430,22 @@
       <c r="I17" s="3"/>
       <c r="J17" s="8"/>
     </row>
-    <row r="18" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A18" s="27">
-        <v>8</v>
-      </c>
-      <c r="B18" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="32"/>
-    </row>
-    <row r="19" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A19" s="31"/>
-      <c r="B19" s="31"/>
-      <c r="C19" s="31">
-        <v>0.995</v>
-      </c>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="6"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="8"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="6"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -6746,19 +9454,19 @@
       <c r="I19" s="3"/>
       <c r="J19" s="8"/>
     </row>
-    <row r="20" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A20" s="36"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="32"/>
-    </row>
-    <row r="21" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="6"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="8"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -6770,19 +9478,19 @@
       <c r="I21" s="3"/>
       <c r="J21" s="8"/>
     </row>
-    <row r="22" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A22" s="36"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="32"/>
-    </row>
-    <row r="23" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="6"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="8"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="6"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -6794,19 +9502,19 @@
       <c r="I23" s="3"/>
       <c r="J23" s="8"/>
     </row>
-    <row r="24" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A24" s="36"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="32"/>
-    </row>
-    <row r="25" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="6"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="8"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="6"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -6818,19 +9526,19 @@
       <c r="I25" s="3"/>
       <c r="J25" s="8"/>
     </row>
-    <row r="26" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A26" s="36"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="32"/>
-    </row>
-    <row r="27" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="6"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="8"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -6842,19 +9550,19 @@
       <c r="I27" s="3"/>
       <c r="J27" s="8"/>
     </row>
-    <row r="28" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A28" s="36"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="32"/>
-    </row>
-    <row r="29" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="6"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="8"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -6866,19 +9574,19 @@
       <c r="I29" s="3"/>
       <c r="J29" s="8"/>
     </row>
-    <row r="30" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A30" s="36"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="32"/>
-    </row>
-    <row r="31" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="6"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="8"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -6890,19 +9598,19 @@
       <c r="I31" s="3"/>
       <c r="J31" s="8"/>
     </row>
-    <row r="32" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A32" s="36"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="32"/>
-    </row>
-    <row r="33" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="8"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="6"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -6914,19 +9622,19 @@
       <c r="I33" s="3"/>
       <c r="J33" s="8"/>
     </row>
-    <row r="34" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A34" s="36"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="32"/>
-    </row>
-    <row r="35" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="6"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="8"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="6"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -6938,19 +9646,19 @@
       <c r="I35" s="3"/>
       <c r="J35" s="8"/>
     </row>
-    <row r="36" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A36" s="36"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="32"/>
-    </row>
-    <row r="37" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="6"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="8"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="6"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -6962,19 +9670,19 @@
       <c r="I37" s="3"/>
       <c r="J37" s="8"/>
     </row>
-    <row r="38" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A38" s="36"/>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="32"/>
-    </row>
-    <row r="39" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="6"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="8"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="6"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -6986,19 +9694,19 @@
       <c r="I39" s="3"/>
       <c r="J39" s="8"/>
     </row>
-    <row r="40" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A40" s="36"/>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="13"/>
-      <c r="J40" s="32"/>
-    </row>
-    <row r="41" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="6"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="8"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="6"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -7010,19 +9718,19 @@
       <c r="I41" s="3"/>
       <c r="J41" s="8"/>
     </row>
-    <row r="42" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A42" s="36"/>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="13"/>
-      <c r="I42" s="13"/>
-      <c r="J42" s="32"/>
-    </row>
-    <row r="43" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="6"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="8"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="6"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -7034,19 +9742,19 @@
       <c r="I43" s="3"/>
       <c r="J43" s="8"/>
     </row>
-    <row r="44" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A44" s="36"/>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
-      <c r="I44" s="13"/>
-      <c r="J44" s="32"/>
-    </row>
-    <row r="45" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="6"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="8"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="6"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -7058,19 +9766,19 @@
       <c r="I45" s="3"/>
       <c r="J45" s="8"/>
     </row>
-    <row r="46" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A46" s="36"/>
-      <c r="B46" s="13"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="13"/>
-      <c r="J46" s="32"/>
-    </row>
-    <row r="47" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="6"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="8"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="6"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -7082,19 +9790,19 @@
       <c r="I47" s="3"/>
       <c r="J47" s="8"/>
     </row>
-    <row r="48" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A48" s="36"/>
-      <c r="B48" s="13"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="13"/>
-      <c r="J48" s="32"/>
-    </row>
-    <row r="49" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="6"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="8"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="6"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -7106,19 +9814,19 @@
       <c r="I49" s="3"/>
       <c r="J49" s="8"/>
     </row>
-    <row r="50" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A50" s="36"/>
-      <c r="B50" s="13"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
-      <c r="I50" s="13"/>
-      <c r="J50" s="32"/>
-    </row>
-    <row r="51" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="6"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="8"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="6"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -7130,19 +9838,19 @@
       <c r="I51" s="3"/>
       <c r="J51" s="8"/>
     </row>
-    <row r="52" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A52" s="36"/>
-      <c r="B52" s="13"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
-      <c r="I52" s="13"/>
-      <c r="J52" s="32"/>
-    </row>
-    <row r="53" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="6"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3"/>
+      <c r="I52" s="3"/>
+      <c r="J52" s="8"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="6"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -7154,19 +9862,19 @@
       <c r="I53" s="3"/>
       <c r="J53" s="8"/>
     </row>
-    <row r="54" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A54" s="36"/>
-      <c r="B54" s="13"/>
-      <c r="C54" s="13"/>
-      <c r="D54" s="13"/>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="13"/>
-      <c r="I54" s="13"/>
-      <c r="J54" s="32"/>
-    </row>
-    <row r="55" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="6"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
+      <c r="J54" s="8"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="6"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -7178,19 +9886,19 @@
       <c r="I55" s="3"/>
       <c r="J55" s="8"/>
     </row>
-    <row r="56" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A56" s="36"/>
-      <c r="B56" s="13"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="13"/>
-      <c r="E56" s="13"/>
-      <c r="F56" s="13"/>
-      <c r="G56" s="13"/>
-      <c r="H56" s="13"/>
-      <c r="I56" s="13"/>
-      <c r="J56" s="32"/>
-    </row>
-    <row r="57" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="6"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
+      <c r="J56" s="8"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="6"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -7202,19 +9910,19 @@
       <c r="I57" s="3"/>
       <c r="J57" s="8"/>
     </row>
-    <row r="58" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A58" s="36"/>
-      <c r="B58" s="13"/>
-      <c r="C58" s="13"/>
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
-      <c r="I58" s="13"/>
-      <c r="J58" s="32"/>
-    </row>
-    <row r="59" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="6"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="H58" s="3"/>
+      <c r="I58" s="3"/>
+      <c r="J58" s="8"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="6"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -7226,19 +9934,19 @@
       <c r="I59" s="3"/>
       <c r="J59" s="8"/>
     </row>
-    <row r="60" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A60" s="36"/>
-      <c r="B60" s="13"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="13"/>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="13"/>
-      <c r="H60" s="13"/>
-      <c r="I60" s="13"/>
-      <c r="J60" s="32"/>
-    </row>
-    <row r="61" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="6"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
+      <c r="I60" s="3"/>
+      <c r="J60" s="8"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="6"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -7250,19 +9958,19 @@
       <c r="I61" s="3"/>
       <c r="J61" s="8"/>
     </row>
-    <row r="62" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A62" s="36"/>
-      <c r="B62" s="13"/>
-      <c r="C62" s="13"/>
-      <c r="D62" s="13"/>
-      <c r="E62" s="13"/>
-      <c r="F62" s="13"/>
-      <c r="G62" s="13"/>
-      <c r="H62" s="13"/>
-      <c r="I62" s="13"/>
-      <c r="J62" s="32"/>
-    </row>
-    <row r="63" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="6"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="3"/>
+      <c r="J62" s="8"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="6"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -7274,19 +9982,19 @@
       <c r="I63" s="3"/>
       <c r="J63" s="8"/>
     </row>
-    <row r="64" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A64" s="36"/>
-      <c r="B64" s="13"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="13"/>
-      <c r="E64" s="13"/>
-      <c r="F64" s="13"/>
-      <c r="G64" s="13"/>
-      <c r="H64" s="13"/>
-      <c r="I64" s="13"/>
-      <c r="J64" s="32"/>
-    </row>
-    <row r="65" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="6"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
+      <c r="H64" s="3"/>
+      <c r="I64" s="3"/>
+      <c r="J64" s="8"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="6"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -7298,19 +10006,19 @@
       <c r="I65" s="3"/>
       <c r="J65" s="8"/>
     </row>
-    <row r="66" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A66" s="36"/>
-      <c r="B66" s="13"/>
-      <c r="C66" s="13"/>
-      <c r="D66" s="13"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="13"/>
-      <c r="H66" s="13"/>
-      <c r="I66" s="13"/>
-      <c r="J66" s="32"/>
-    </row>
-    <row r="67" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="6"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
+      <c r="H66" s="3"/>
+      <c r="I66" s="3"/>
+      <c r="J66" s="8"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="6"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -7322,19 +10030,19 @@
       <c r="I67" s="3"/>
       <c r="J67" s="8"/>
     </row>
-    <row r="68" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A68" s="36"/>
-      <c r="B68" s="13"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13"/>
-      <c r="H68" s="13"/>
-      <c r="I68" s="13"/>
-      <c r="J68" s="32"/>
-    </row>
-    <row r="69" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" s="6"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="H68" s="3"/>
+      <c r="I68" s="3"/>
+      <c r="J68" s="8"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="6"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -7346,19 +10054,19 @@
       <c r="I69" s="3"/>
       <c r="J69" s="8"/>
     </row>
-    <row r="70" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A70" s="36"/>
-      <c r="B70" s="13"/>
-      <c r="C70" s="13"/>
-      <c r="D70" s="13"/>
-      <c r="E70" s="13"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="13"/>
-      <c r="J70" s="32"/>
-    </row>
-    <row r="71" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" s="6"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="3"/>
+      <c r="J70" s="8"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="6"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -7370,19 +10078,19 @@
       <c r="I71" s="3"/>
       <c r="J71" s="8"/>
     </row>
-    <row r="72" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A72" s="36"/>
-      <c r="B72" s="13"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="13"/>
-      <c r="J72" s="32"/>
-    </row>
-    <row r="73" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="6"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="3"/>
+      <c r="I72" s="3"/>
+      <c r="J72" s="8"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="6"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -7394,19 +10102,19 @@
       <c r="I73" s="3"/>
       <c r="J73" s="8"/>
     </row>
-    <row r="74" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A74" s="36"/>
-      <c r="B74" s="13"/>
-      <c r="C74" s="13"/>
-      <c r="D74" s="13"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="13"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="13"/>
-      <c r="I74" s="13"/>
-      <c r="J74" s="32"/>
-    </row>
-    <row r="75" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" s="6"/>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="3"/>
+      <c r="J74" s="8"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="6"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -7418,19 +10126,19 @@
       <c r="I75" s="3"/>
       <c r="J75" s="8"/>
     </row>
-    <row r="76" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A76" s="36"/>
-      <c r="B76" s="13"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="13"/>
-      <c r="E76" s="13"/>
-      <c r="F76" s="13"/>
-      <c r="G76" s="13"/>
-      <c r="H76" s="13"/>
-      <c r="I76" s="13"/>
-      <c r="J76" s="32"/>
-    </row>
-    <row r="77" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" s="6"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="3"/>
+      <c r="J76" s="8"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="6"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -7442,19 +10150,19 @@
       <c r="I77" s="3"/>
       <c r="J77" s="8"/>
     </row>
-    <row r="78" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A78" s="36"/>
-      <c r="B78" s="13"/>
-      <c r="C78" s="13"/>
-      <c r="D78" s="13"/>
-      <c r="E78" s="13"/>
-      <c r="F78" s="13"/>
-      <c r="G78" s="13"/>
-      <c r="H78" s="13"/>
-      <c r="I78" s="13"/>
-      <c r="J78" s="32"/>
-    </row>
-    <row r="79" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" s="6"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3"/>
+      <c r="I78" s="3"/>
+      <c r="J78" s="8"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="6"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -7466,19 +10174,19 @@
       <c r="I79" s="3"/>
       <c r="J79" s="8"/>
     </row>
-    <row r="80" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A80" s="36"/>
-      <c r="B80" s="13"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="13"/>
-      <c r="E80" s="13"/>
-      <c r="F80" s="13"/>
-      <c r="G80" s="13"/>
-      <c r="H80" s="13"/>
-      <c r="I80" s="13"/>
-      <c r="J80" s="32"/>
-    </row>
-    <row r="81" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" s="6"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
+      <c r="H80" s="3"/>
+      <c r="I80" s="3"/>
+      <c r="J80" s="8"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="6"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -7490,19 +10198,19 @@
       <c r="I81" s="3"/>
       <c r="J81" s="8"/>
     </row>
-    <row r="82" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A82" s="36"/>
-      <c r="B82" s="13"/>
-      <c r="C82" s="13"/>
-      <c r="D82" s="13"/>
-      <c r="E82" s="13"/>
-      <c r="F82" s="13"/>
-      <c r="G82" s="13"/>
-      <c r="H82" s="13"/>
-      <c r="I82" s="13"/>
-      <c r="J82" s="32"/>
-    </row>
-    <row r="83" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" s="6"/>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
+      <c r="H82" s="3"/>
+      <c r="I82" s="3"/>
+      <c r="J82" s="8"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="6"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -7514,19 +10222,19 @@
       <c r="I83" s="3"/>
       <c r="J83" s="8"/>
     </row>
-    <row r="84" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A84" s="36"/>
-      <c r="B84" s="13"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="13"/>
-      <c r="E84" s="13"/>
-      <c r="F84" s="13"/>
-      <c r="G84" s="13"/>
-      <c r="H84" s="13"/>
-      <c r="I84" s="13"/>
-      <c r="J84" s="32"/>
-    </row>
-    <row r="85" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" s="6"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
+      <c r="H84" s="3"/>
+      <c r="I84" s="3"/>
+      <c r="J84" s="8"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="6"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -7538,19 +10246,19 @@
       <c r="I85" s="3"/>
       <c r="J85" s="8"/>
     </row>
-    <row r="86" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A86" s="36"/>
-      <c r="B86" s="13"/>
-      <c r="C86" s="13"/>
-      <c r="D86" s="13"/>
-      <c r="E86" s="13"/>
-      <c r="F86" s="13"/>
-      <c r="G86" s="13"/>
-      <c r="H86" s="13"/>
-      <c r="I86" s="13"/>
-      <c r="J86" s="32"/>
-    </row>
-    <row r="87" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" s="6"/>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
+      <c r="H86" s="3"/>
+      <c r="I86" s="3"/>
+      <c r="J86" s="8"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="6"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -7562,19 +10270,19 @@
       <c r="I87" s="3"/>
       <c r="J87" s="8"/>
     </row>
-    <row r="88" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A88" s="36"/>
-      <c r="B88" s="13"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="13"/>
-      <c r="E88" s="13"/>
-      <c r="F88" s="13"/>
-      <c r="G88" s="13"/>
-      <c r="H88" s="13"/>
-      <c r="I88" s="13"/>
-      <c r="J88" s="32"/>
-    </row>
-    <row r="89" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" s="6"/>
+      <c r="B88" s="3"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
+      <c r="H88" s="3"/>
+      <c r="I88" s="3"/>
+      <c r="J88" s="8"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="6"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -7586,19 +10294,19 @@
       <c r="I89" s="3"/>
       <c r="J89" s="8"/>
     </row>
-    <row r="90" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A90" s="36"/>
-      <c r="B90" s="13"/>
-      <c r="C90" s="13"/>
-      <c r="D90" s="13"/>
-      <c r="E90" s="13"/>
-      <c r="F90" s="13"/>
-      <c r="G90" s="13"/>
-      <c r="H90" s="13"/>
-      <c r="I90" s="13"/>
-      <c r="J90" s="32"/>
-    </row>
-    <row r="91" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90" s="6"/>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+      <c r="H90" s="3"/>
+      <c r="I90" s="3"/>
+      <c r="J90" s="8"/>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="6"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -7610,19 +10318,19 @@
       <c r="I91" s="3"/>
       <c r="J91" s="8"/>
     </row>
-    <row r="92" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A92" s="36"/>
-      <c r="B92" s="13"/>
-      <c r="C92" s="13"/>
-      <c r="D92" s="13"/>
-      <c r="E92" s="13"/>
-      <c r="F92" s="13"/>
-      <c r="G92" s="13"/>
-      <c r="H92" s="13"/>
-      <c r="I92" s="13"/>
-      <c r="J92" s="32"/>
-    </row>
-    <row r="93" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92" s="6"/>
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
+      <c r="H92" s="3"/>
+      <c r="I92" s="3"/>
+      <c r="J92" s="8"/>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="6"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -7634,19 +10342,19 @@
       <c r="I93" s="3"/>
       <c r="J93" s="8"/>
     </row>
-    <row r="94" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A94" s="36"/>
-      <c r="B94" s="13"/>
-      <c r="C94" s="13"/>
-      <c r="D94" s="13"/>
-      <c r="E94" s="13"/>
-      <c r="F94" s="13"/>
-      <c r="G94" s="13"/>
-      <c r="H94" s="13"/>
-      <c r="I94" s="13"/>
-      <c r="J94" s="32"/>
-    </row>
-    <row r="95" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94" s="6"/>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
+      <c r="H94" s="3"/>
+      <c r="I94" s="3"/>
+      <c r="J94" s="8"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="6"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -7658,19 +10366,19 @@
       <c r="I95" s="3"/>
       <c r="J95" s="8"/>
     </row>
-    <row r="96" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A96" s="36"/>
-      <c r="B96" s="13"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="13"/>
-      <c r="E96" s="13"/>
-      <c r="F96" s="13"/>
-      <c r="G96" s="13"/>
-      <c r="H96" s="13"/>
-      <c r="I96" s="13"/>
-      <c r="J96" s="32"/>
-    </row>
-    <row r="97" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" s="6"/>
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
+      <c r="H96" s="3"/>
+      <c r="I96" s="3"/>
+      <c r="J96" s="8"/>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="6"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -7682,19 +10390,19 @@
       <c r="I97" s="3"/>
       <c r="J97" s="8"/>
     </row>
-    <row r="98" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A98" s="36"/>
-      <c r="B98" s="13"/>
-      <c r="C98" s="13"/>
-      <c r="D98" s="13"/>
-      <c r="E98" s="13"/>
-      <c r="F98" s="13"/>
-      <c r="G98" s="13"/>
-      <c r="H98" s="13"/>
-      <c r="I98" s="13"/>
-      <c r="J98" s="32"/>
-    </row>
-    <row r="99" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" s="6"/>
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+      <c r="H98" s="3"/>
+      <c r="I98" s="3"/>
+      <c r="J98" s="8"/>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="6"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -7706,19 +10414,19 @@
       <c r="I99" s="3"/>
       <c r="J99" s="8"/>
     </row>
-    <row r="100" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A100" s="36"/>
-      <c r="B100" s="13"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="13"/>
-      <c r="E100" s="13"/>
-      <c r="F100" s="13"/>
-      <c r="G100" s="13"/>
-      <c r="H100" s="13"/>
-      <c r="I100" s="13"/>
-      <c r="J100" s="32"/>
-    </row>
-    <row r="101" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100" s="6"/>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
+      <c r="H100" s="3"/>
+      <c r="I100" s="3"/>
+      <c r="J100" s="8"/>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="6"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -7730,19 +10438,19 @@
       <c r="I101" s="3"/>
       <c r="J101" s="8"/>
     </row>
-    <row r="102" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A102" s="36"/>
-      <c r="B102" s="13"/>
-      <c r="C102" s="13"/>
-      <c r="D102" s="13"/>
-      <c r="E102" s="13"/>
-      <c r="F102" s="13"/>
-      <c r="G102" s="13"/>
-      <c r="H102" s="13"/>
-      <c r="I102" s="13"/>
-      <c r="J102" s="32"/>
-    </row>
-    <row r="103" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102" s="6"/>
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3"/>
+      <c r="H102" s="3"/>
+      <c r="I102" s="3"/>
+      <c r="J102" s="8"/>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="6"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -7754,19 +10462,19 @@
       <c r="I103" s="3"/>
       <c r="J103" s="8"/>
     </row>
-    <row r="104" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A104" s="36"/>
-      <c r="B104" s="13"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="13"/>
-      <c r="E104" s="13"/>
-      <c r="F104" s="13"/>
-      <c r="G104" s="13"/>
-      <c r="H104" s="13"/>
-      <c r="I104" s="13"/>
-      <c r="J104" s="32"/>
-    </row>
-    <row r="105" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" s="6"/>
+      <c r="B104" s="3"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="3"/>
+      <c r="F104" s="3"/>
+      <c r="G104" s="3"/>
+      <c r="H104" s="3"/>
+      <c r="I104" s="3"/>
+      <c r="J104" s="8"/>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="6"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -7778,19 +10486,19 @@
       <c r="I105" s="3"/>
       <c r="J105" s="8"/>
     </row>
-    <row r="106" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A106" s="36"/>
-      <c r="B106" s="13"/>
-      <c r="C106" s="13"/>
-      <c r="D106" s="13"/>
-      <c r="E106" s="13"/>
-      <c r="F106" s="13"/>
-      <c r="G106" s="13"/>
-      <c r="H106" s="13"/>
-      <c r="I106" s="13"/>
-      <c r="J106" s="32"/>
-    </row>
-    <row r="107" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106" s="6"/>
+      <c r="B106" s="3"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3"/>
+      <c r="H106" s="3"/>
+      <c r="I106" s="3"/>
+      <c r="J106" s="8"/>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="6"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -7802,19 +10510,19 @@
       <c r="I107" s="3"/>
       <c r="J107" s="8"/>
     </row>
-    <row r="108" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A108" s="36"/>
-      <c r="B108" s="13"/>
-      <c r="C108" s="13"/>
-      <c r="D108" s="13"/>
-      <c r="E108" s="13"/>
-      <c r="F108" s="13"/>
-      <c r="G108" s="13"/>
-      <c r="H108" s="13"/>
-      <c r="I108" s="13"/>
-      <c r="J108" s="32"/>
-    </row>
-    <row r="109" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" s="6"/>
+      <c r="B108" s="3"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="3"/>
+      <c r="F108" s="3"/>
+      <c r="G108" s="3"/>
+      <c r="H108" s="3"/>
+      <c r="I108" s="3"/>
+      <c r="J108" s="8"/>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="6"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -7826,19 +10534,19 @@
       <c r="I109" s="3"/>
       <c r="J109" s="8"/>
     </row>
-    <row r="110" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A110" s="36"/>
-      <c r="B110" s="13"/>
-      <c r="C110" s="13"/>
-      <c r="D110" s="13"/>
-      <c r="E110" s="13"/>
-      <c r="F110" s="13"/>
-      <c r="G110" s="13"/>
-      <c r="H110" s="13"/>
-      <c r="I110" s="13"/>
-      <c r="J110" s="32"/>
-    </row>
-    <row r="111" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A110" s="6"/>
+      <c r="B110" s="3"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3"/>
+      <c r="H110" s="3"/>
+      <c r="I110" s="3"/>
+      <c r="J110" s="8"/>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="6"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -7850,19 +10558,19 @@
       <c r="I111" s="3"/>
       <c r="J111" s="8"/>
     </row>
-    <row r="112" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A112" s="36"/>
-      <c r="B112" s="13"/>
-      <c r="C112" s="13"/>
-      <c r="D112" s="13"/>
-      <c r="E112" s="13"/>
-      <c r="F112" s="13"/>
-      <c r="G112" s="13"/>
-      <c r="H112" s="13"/>
-      <c r="I112" s="13"/>
-      <c r="J112" s="32"/>
-    </row>
-    <row r="113" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A112" s="6"/>
+      <c r="B112" s="3"/>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3"/>
+      <c r="E112" s="3"/>
+      <c r="F112" s="3"/>
+      <c r="G112" s="3"/>
+      <c r="H112" s="3"/>
+      <c r="I112" s="3"/>
+      <c r="J112" s="8"/>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="6"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -7874,19 +10582,19 @@
       <c r="I113" s="3"/>
       <c r="J113" s="8"/>
     </row>
-    <row r="114" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A114" s="36"/>
-      <c r="B114" s="13"/>
-      <c r="C114" s="13"/>
-      <c r="D114" s="13"/>
-      <c r="E114" s="13"/>
-      <c r="F114" s="13"/>
-      <c r="G114" s="13"/>
-      <c r="H114" s="13"/>
-      <c r="I114" s="13"/>
-      <c r="J114" s="32"/>
-    </row>
-    <row r="115" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A114" s="6"/>
+      <c r="B114" s="3"/>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="3"/>
+      <c r="F114" s="3"/>
+      <c r="G114" s="3"/>
+      <c r="H114" s="3"/>
+      <c r="I114" s="3"/>
+      <c r="J114" s="8"/>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="6"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -7898,19 +10606,19 @@
       <c r="I115" s="3"/>
       <c r="J115" s="8"/>
     </row>
-    <row r="116" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A116" s="36"/>
-      <c r="B116" s="13"/>
-      <c r="C116" s="13"/>
-      <c r="D116" s="13"/>
-      <c r="E116" s="13"/>
-      <c r="F116" s="13"/>
-      <c r="G116" s="13"/>
-      <c r="H116" s="13"/>
-      <c r="I116" s="13"/>
-      <c r="J116" s="32"/>
-    </row>
-    <row r="117" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A116" s="6"/>
+      <c r="B116" s="3"/>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="3"/>
+      <c r="F116" s="3"/>
+      <c r="G116" s="3"/>
+      <c r="H116" s="3"/>
+      <c r="I116" s="3"/>
+      <c r="J116" s="8"/>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="6"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -7922,19 +10630,19 @@
       <c r="I117" s="3"/>
       <c r="J117" s="8"/>
     </row>
-    <row r="118" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A118" s="36"/>
-      <c r="B118" s="13"/>
-      <c r="C118" s="13"/>
-      <c r="D118" s="13"/>
-      <c r="E118" s="13"/>
-      <c r="F118" s="13"/>
-      <c r="G118" s="13"/>
-      <c r="H118" s="13"/>
-      <c r="I118" s="13"/>
-      <c r="J118" s="32"/>
-    </row>
-    <row r="119" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A118" s="6"/>
+      <c r="B118" s="3"/>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="3"/>
+      <c r="F118" s="3"/>
+      <c r="G118" s="3"/>
+      <c r="H118" s="3"/>
+      <c r="I118" s="3"/>
+      <c r="J118" s="8"/>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="6"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -7946,19 +10654,19 @@
       <c r="I119" s="3"/>
       <c r="J119" s="8"/>
     </row>
-    <row r="120" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A120" s="36"/>
-      <c r="B120" s="13"/>
-      <c r="C120" s="13"/>
-      <c r="D120" s="13"/>
-      <c r="E120" s="13"/>
-      <c r="F120" s="13"/>
-      <c r="G120" s="13"/>
-      <c r="H120" s="13"/>
-      <c r="I120" s="13"/>
-      <c r="J120" s="32"/>
-    </row>
-    <row r="121" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A120" s="6"/>
+      <c r="B120" s="3"/>
+      <c r="C120" s="3"/>
+      <c r="D120" s="3"/>
+      <c r="E120" s="3"/>
+      <c r="F120" s="3"/>
+      <c r="G120" s="3"/>
+      <c r="H120" s="3"/>
+      <c r="I120" s="3"/>
+      <c r="J120" s="8"/>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="6"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -7970,19 +10678,19 @@
       <c r="I121" s="3"/>
       <c r="J121" s="8"/>
     </row>
-    <row r="122" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A122" s="36"/>
-      <c r="B122" s="13"/>
-      <c r="C122" s="13"/>
-      <c r="D122" s="13"/>
-      <c r="E122" s="13"/>
-      <c r="F122" s="13"/>
-      <c r="G122" s="13"/>
-      <c r="H122" s="13"/>
-      <c r="I122" s="13"/>
-      <c r="J122" s="32"/>
-    </row>
-    <row r="123" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A122" s="6"/>
+      <c r="B122" s="3"/>
+      <c r="C122" s="3"/>
+      <c r="D122" s="3"/>
+      <c r="E122" s="3"/>
+      <c r="F122" s="3"/>
+      <c r="G122" s="3"/>
+      <c r="H122" s="3"/>
+      <c r="I122" s="3"/>
+      <c r="J122" s="8"/>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="6"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -7994,19 +10702,19 @@
       <c r="I123" s="3"/>
       <c r="J123" s="8"/>
     </row>
-    <row r="124" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A124" s="36"/>
-      <c r="B124" s="13"/>
-      <c r="C124" s="13"/>
-      <c r="D124" s="13"/>
-      <c r="E124" s="13"/>
-      <c r="F124" s="13"/>
-      <c r="G124" s="13"/>
-      <c r="H124" s="13"/>
-      <c r="I124" s="13"/>
-      <c r="J124" s="32"/>
-    </row>
-    <row r="125" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A124" s="6"/>
+      <c r="B124" s="3"/>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3"/>
+      <c r="E124" s="3"/>
+      <c r="F124" s="3"/>
+      <c r="G124" s="3"/>
+      <c r="H124" s="3"/>
+      <c r="I124" s="3"/>
+      <c r="J124" s="8"/>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="6"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -8018,19 +10726,19 @@
       <c r="I125" s="3"/>
       <c r="J125" s="8"/>
     </row>
-    <row r="126" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A126" s="36"/>
-      <c r="B126" s="13"/>
-      <c r="C126" s="13"/>
-      <c r="D126" s="13"/>
-      <c r="E126" s="13"/>
-      <c r="F126" s="13"/>
-      <c r="G126" s="13"/>
-      <c r="H126" s="13"/>
-      <c r="I126" s="13"/>
-      <c r="J126" s="32"/>
-    </row>
-    <row r="127" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A126" s="6"/>
+      <c r="B126" s="3"/>
+      <c r="C126" s="3"/>
+      <c r="D126" s="3"/>
+      <c r="E126" s="3"/>
+      <c r="F126" s="3"/>
+      <c r="G126" s="3"/>
+      <c r="H126" s="3"/>
+      <c r="I126" s="3"/>
+      <c r="J126" s="8"/>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="6"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -8042,19 +10750,19 @@
       <c r="I127" s="3"/>
       <c r="J127" s="8"/>
     </row>
-    <row r="128" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A128" s="36"/>
-      <c r="B128" s="13"/>
-      <c r="C128" s="13"/>
-      <c r="D128" s="13"/>
-      <c r="E128" s="13"/>
-      <c r="F128" s="13"/>
-      <c r="G128" s="13"/>
-      <c r="H128" s="13"/>
-      <c r="I128" s="13"/>
-      <c r="J128" s="32"/>
-    </row>
-    <row r="129" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A128" s="6"/>
+      <c r="B128" s="3"/>
+      <c r="C128" s="3"/>
+      <c r="D128" s="3"/>
+      <c r="E128" s="3"/>
+      <c r="F128" s="3"/>
+      <c r="G128" s="3"/>
+      <c r="H128" s="3"/>
+      <c r="I128" s="3"/>
+      <c r="J128" s="8"/>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="6"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -8066,19 +10774,19 @@
       <c r="I129" s="3"/>
       <c r="J129" s="8"/>
     </row>
-    <row r="130" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A130" s="36"/>
-      <c r="B130" s="13"/>
-      <c r="C130" s="13"/>
-      <c r="D130" s="13"/>
-      <c r="E130" s="13"/>
-      <c r="F130" s="13"/>
-      <c r="G130" s="13"/>
-      <c r="H130" s="13"/>
-      <c r="I130" s="13"/>
-      <c r="J130" s="32"/>
-    </row>
-    <row r="131" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A130" s="6"/>
+      <c r="B130" s="3"/>
+      <c r="C130" s="3"/>
+      <c r="D130" s="3"/>
+      <c r="E130" s="3"/>
+      <c r="F130" s="3"/>
+      <c r="G130" s="3"/>
+      <c r="H130" s="3"/>
+      <c r="I130" s="3"/>
+      <c r="J130" s="8"/>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="6"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -8090,19 +10798,19 @@
       <c r="I131" s="3"/>
       <c r="J131" s="8"/>
     </row>
-    <row r="132" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A132" s="36"/>
-      <c r="B132" s="13"/>
-      <c r="C132" s="13"/>
-      <c r="D132" s="13"/>
-      <c r="E132" s="13"/>
-      <c r="F132" s="13"/>
-      <c r="G132" s="13"/>
-      <c r="H132" s="13"/>
-      <c r="I132" s="13"/>
-      <c r="J132" s="32"/>
-    </row>
-    <row r="133" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A132" s="6"/>
+      <c r="B132" s="3"/>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3"/>
+      <c r="E132" s="3"/>
+      <c r="F132" s="3"/>
+      <c r="G132" s="3"/>
+      <c r="H132" s="3"/>
+      <c r="I132" s="3"/>
+      <c r="J132" s="8"/>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="6"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -8114,19 +10822,19 @@
       <c r="I133" s="3"/>
       <c r="J133" s="8"/>
     </row>
-    <row r="134" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A134" s="36"/>
-      <c r="B134" s="13"/>
-      <c r="C134" s="13"/>
-      <c r="D134" s="13"/>
-      <c r="E134" s="13"/>
-      <c r="F134" s="13"/>
-      <c r="G134" s="13"/>
-      <c r="H134" s="13"/>
-      <c r="I134" s="13"/>
-      <c r="J134" s="32"/>
-    </row>
-    <row r="135" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A134" s="6"/>
+      <c r="B134" s="3"/>
+      <c r="C134" s="3"/>
+      <c r="D134" s="3"/>
+      <c r="E134" s="3"/>
+      <c r="F134" s="3"/>
+      <c r="G134" s="3"/>
+      <c r="H134" s="3"/>
+      <c r="I134" s="3"/>
+      <c r="J134" s="8"/>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="6"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
@@ -8138,19 +10846,19 @@
       <c r="I135" s="3"/>
       <c r="J135" s="8"/>
     </row>
-    <row r="136" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A136" s="36"/>
-      <c r="B136" s="13"/>
-      <c r="C136" s="13"/>
-      <c r="D136" s="13"/>
-      <c r="E136" s="13"/>
-      <c r="F136" s="13"/>
-      <c r="G136" s="13"/>
-      <c r="H136" s="13"/>
-      <c r="I136" s="13"/>
-      <c r="J136" s="32"/>
-    </row>
-    <row r="137" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A136" s="6"/>
+      <c r="B136" s="3"/>
+      <c r="C136" s="3"/>
+      <c r="D136" s="3"/>
+      <c r="E136" s="3"/>
+      <c r="F136" s="3"/>
+      <c r="G136" s="3"/>
+      <c r="H136" s="3"/>
+      <c r="I136" s="3"/>
+      <c r="J136" s="8"/>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="6"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -8162,19 +10870,19 @@
       <c r="I137" s="3"/>
       <c r="J137" s="8"/>
     </row>
-    <row r="138" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A138" s="36"/>
-      <c r="B138" s="13"/>
-      <c r="C138" s="13"/>
-      <c r="D138" s="13"/>
-      <c r="E138" s="13"/>
-      <c r="F138" s="13"/>
-      <c r="G138" s="13"/>
-      <c r="H138" s="13"/>
-      <c r="I138" s="13"/>
-      <c r="J138" s="32"/>
-    </row>
-    <row r="139" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A138" s="6"/>
+      <c r="B138" s="3"/>
+      <c r="C138" s="3"/>
+      <c r="D138" s="3"/>
+      <c r="E138" s="3"/>
+      <c r="F138" s="3"/>
+      <c r="G138" s="3"/>
+      <c r="H138" s="3"/>
+      <c r="I138" s="3"/>
+      <c r="J138" s="8"/>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" s="6"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
@@ -8186,19 +10894,19 @@
       <c r="I139" s="3"/>
       <c r="J139" s="8"/>
     </row>
-    <row r="140" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A140" s="36"/>
-      <c r="B140" s="13"/>
-      <c r="C140" s="13"/>
-      <c r="D140" s="13"/>
-      <c r="E140" s="13"/>
-      <c r="F140" s="13"/>
-      <c r="G140" s="13"/>
-      <c r="H140" s="13"/>
-      <c r="I140" s="13"/>
-      <c r="J140" s="32"/>
-    </row>
-    <row r="141" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A140" s="6"/>
+      <c r="B140" s="3"/>
+      <c r="C140" s="3"/>
+      <c r="D140" s="3"/>
+      <c r="E140" s="3"/>
+      <c r="F140" s="3"/>
+      <c r="G140" s="3"/>
+      <c r="H140" s="3"/>
+      <c r="I140" s="3"/>
+      <c r="J140" s="8"/>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" s="6"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
@@ -8210,19 +10918,19 @@
       <c r="I141" s="3"/>
       <c r="J141" s="8"/>
     </row>
-    <row r="142" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A142" s="36"/>
-      <c r="B142" s="13"/>
-      <c r="C142" s="13"/>
-      <c r="D142" s="13"/>
-      <c r="E142" s="13"/>
-      <c r="F142" s="13"/>
-      <c r="G142" s="13"/>
-      <c r="H142" s="13"/>
-      <c r="I142" s="13"/>
-      <c r="J142" s="32"/>
-    </row>
-    <row r="143" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A142" s="6"/>
+      <c r="B142" s="3"/>
+      <c r="C142" s="3"/>
+      <c r="D142" s="3"/>
+      <c r="E142" s="3"/>
+      <c r="F142" s="3"/>
+      <c r="G142" s="3"/>
+      <c r="H142" s="3"/>
+      <c r="I142" s="3"/>
+      <c r="J142" s="8"/>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="6"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
@@ -8234,19 +10942,19 @@
       <c r="I143" s="3"/>
       <c r="J143" s="8"/>
     </row>
-    <row r="144" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A144" s="36"/>
-      <c r="B144" s="13"/>
-      <c r="C144" s="13"/>
-      <c r="D144" s="13"/>
-      <c r="E144" s="13"/>
-      <c r="F144" s="13"/>
-      <c r="G144" s="13"/>
-      <c r="H144" s="13"/>
-      <c r="I144" s="13"/>
-      <c r="J144" s="32"/>
-    </row>
-    <row r="145" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A144" s="6"/>
+      <c r="B144" s="3"/>
+      <c r="C144" s="3"/>
+      <c r="D144" s="3"/>
+      <c r="E144" s="3"/>
+      <c r="F144" s="3"/>
+      <c r="G144" s="3"/>
+      <c r="H144" s="3"/>
+      <c r="I144" s="3"/>
+      <c r="J144" s="8"/>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="6"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
@@ -8258,19 +10966,19 @@
       <c r="I145" s="3"/>
       <c r="J145" s="8"/>
     </row>
-    <row r="146" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A146" s="36"/>
-      <c r="B146" s="13"/>
-      <c r="C146" s="13"/>
-      <c r="D146" s="13"/>
-      <c r="E146" s="13"/>
-      <c r="F146" s="13"/>
-      <c r="G146" s="13"/>
-      <c r="H146" s="13"/>
-      <c r="I146" s="13"/>
-      <c r="J146" s="32"/>
-    </row>
-    <row r="147" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A146" s="6"/>
+      <c r="B146" s="3"/>
+      <c r="C146" s="3"/>
+      <c r="D146" s="3"/>
+      <c r="E146" s="3"/>
+      <c r="F146" s="3"/>
+      <c r="G146" s="3"/>
+      <c r="H146" s="3"/>
+      <c r="I146" s="3"/>
+      <c r="J146" s="8"/>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="6"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
@@ -8282,19 +10990,19 @@
       <c r="I147" s="3"/>
       <c r="J147" s="8"/>
     </row>
-    <row r="148" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A148" s="36"/>
-      <c r="B148" s="13"/>
-      <c r="C148" s="13"/>
-      <c r="D148" s="13"/>
-      <c r="E148" s="13"/>
-      <c r="F148" s="13"/>
-      <c r="G148" s="13"/>
-      <c r="H148" s="13"/>
-      <c r="I148" s="13"/>
-      <c r="J148" s="32"/>
-    </row>
-    <row r="149" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A148" s="6"/>
+      <c r="B148" s="3"/>
+      <c r="C148" s="3"/>
+      <c r="D148" s="3"/>
+      <c r="E148" s="3"/>
+      <c r="F148" s="3"/>
+      <c r="G148" s="3"/>
+      <c r="H148" s="3"/>
+      <c r="I148" s="3"/>
+      <c r="J148" s="8"/>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" s="6"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
@@ -8306,19 +11014,19 @@
       <c r="I149" s="3"/>
       <c r="J149" s="8"/>
     </row>
-    <row r="150" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A150" s="36"/>
-      <c r="B150" s="13"/>
-      <c r="C150" s="13"/>
-      <c r="D150" s="13"/>
-      <c r="E150" s="13"/>
-      <c r="F150" s="13"/>
-      <c r="G150" s="13"/>
-      <c r="H150" s="13"/>
-      <c r="I150" s="13"/>
-      <c r="J150" s="32"/>
-    </row>
-    <row r="151" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A150" s="6"/>
+      <c r="B150" s="3"/>
+      <c r="C150" s="3"/>
+      <c r="D150" s="3"/>
+      <c r="E150" s="3"/>
+      <c r="F150" s="3"/>
+      <c r="G150" s="3"/>
+      <c r="H150" s="3"/>
+      <c r="I150" s="3"/>
+      <c r="J150" s="8"/>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" s="6"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
@@ -8330,19 +11038,19 @@
       <c r="I151" s="3"/>
       <c r="J151" s="8"/>
     </row>
-    <row r="152" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A152" s="36"/>
-      <c r="B152" s="13"/>
-      <c r="C152" s="13"/>
-      <c r="D152" s="13"/>
-      <c r="E152" s="13"/>
-      <c r="F152" s="13"/>
-      <c r="G152" s="13"/>
-      <c r="H152" s="13"/>
-      <c r="I152" s="13"/>
-      <c r="J152" s="32"/>
-    </row>
-    <row r="153" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A152" s="6"/>
+      <c r="B152" s="3"/>
+      <c r="C152" s="3"/>
+      <c r="D152" s="3"/>
+      <c r="E152" s="3"/>
+      <c r="F152" s="3"/>
+      <c r="G152" s="3"/>
+      <c r="H152" s="3"/>
+      <c r="I152" s="3"/>
+      <c r="J152" s="8"/>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="6"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
@@ -8354,19 +11062,19 @@
       <c r="I153" s="3"/>
       <c r="J153" s="8"/>
     </row>
-    <row r="154" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A154" s="36"/>
-      <c r="B154" s="13"/>
-      <c r="C154" s="13"/>
-      <c r="D154" s="13"/>
-      <c r="E154" s="13"/>
-      <c r="F154" s="13"/>
-      <c r="G154" s="13"/>
-      <c r="H154" s="13"/>
-      <c r="I154" s="13"/>
-      <c r="J154" s="32"/>
-    </row>
-    <row r="155" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A154" s="6"/>
+      <c r="B154" s="3"/>
+      <c r="C154" s="3"/>
+      <c r="D154" s="3"/>
+      <c r="E154" s="3"/>
+      <c r="F154" s="3"/>
+      <c r="G154" s="3"/>
+      <c r="H154" s="3"/>
+      <c r="I154" s="3"/>
+      <c r="J154" s="8"/>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" s="6"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
@@ -8378,19 +11086,19 @@
       <c r="I155" s="3"/>
       <c r="J155" s="8"/>
     </row>
-    <row r="156" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A156" s="36"/>
-      <c r="B156" s="13"/>
-      <c r="C156" s="13"/>
-      <c r="D156" s="13"/>
-      <c r="E156" s="13"/>
-      <c r="F156" s="13"/>
-      <c r="G156" s="13"/>
-      <c r="H156" s="13"/>
-      <c r="I156" s="13"/>
-      <c r="J156" s="32"/>
-    </row>
-    <row r="157" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A156" s="6"/>
+      <c r="B156" s="3"/>
+      <c r="C156" s="3"/>
+      <c r="D156" s="3"/>
+      <c r="E156" s="3"/>
+      <c r="F156" s="3"/>
+      <c r="G156" s="3"/>
+      <c r="H156" s="3"/>
+      <c r="I156" s="3"/>
+      <c r="J156" s="8"/>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" s="6"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
@@ -8402,19 +11110,19 @@
       <c r="I157" s="3"/>
       <c r="J157" s="8"/>
     </row>
-    <row r="158" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A158" s="36"/>
-      <c r="B158" s="13"/>
-      <c r="C158" s="13"/>
-      <c r="D158" s="13"/>
-      <c r="E158" s="13"/>
-      <c r="F158" s="13"/>
-      <c r="G158" s="13"/>
-      <c r="H158" s="13"/>
-      <c r="I158" s="13"/>
-      <c r="J158" s="32"/>
-    </row>
-    <row r="159" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A158" s="6"/>
+      <c r="B158" s="3"/>
+      <c r="C158" s="3"/>
+      <c r="D158" s="3"/>
+      <c r="E158" s="3"/>
+      <c r="F158" s="3"/>
+      <c r="G158" s="3"/>
+      <c r="H158" s="3"/>
+      <c r="I158" s="3"/>
+      <c r="J158" s="8"/>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" s="6"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
@@ -8426,303 +11134,58 @@
       <c r="I159" s="3"/>
       <c r="J159" s="8"/>
     </row>
-    <row r="160" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A160" s="36"/>
-      <c r="B160" s="13"/>
-      <c r="C160" s="13"/>
-      <c r="D160" s="13"/>
-      <c r="E160" s="13"/>
-      <c r="F160" s="13"/>
-      <c r="G160" s="13"/>
-      <c r="H160" s="13"/>
-      <c r="I160" s="13"/>
-      <c r="J160" s="32"/>
-    </row>
-    <row r="161" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A161" s="6"/>
-      <c r="B161" s="3"/>
-      <c r="C161" s="3"/>
-      <c r="D161" s="3"/>
-      <c r="E161" s="3"/>
-      <c r="F161" s="3"/>
-      <c r="G161" s="3"/>
-      <c r="H161" s="3"/>
-      <c r="I161" s="3"/>
-      <c r="J161" s="8"/>
-    </row>
-    <row r="162" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A162" s="36"/>
-      <c r="B162" s="13"/>
-      <c r="C162" s="13"/>
-      <c r="D162" s="13"/>
-      <c r="E162" s="13"/>
-      <c r="F162" s="13"/>
-      <c r="G162" s="13"/>
-      <c r="H162" s="13"/>
-      <c r="I162" s="13"/>
-      <c r="J162" s="32"/>
-    </row>
-    <row r="163" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A163" s="6"/>
-      <c r="B163" s="3"/>
-      <c r="C163" s="3"/>
-      <c r="D163" s="3"/>
-      <c r="E163" s="3"/>
-      <c r="F163" s="3"/>
-      <c r="G163" s="3"/>
-      <c r="H163" s="3"/>
-      <c r="I163" s="3"/>
-      <c r="J163" s="8"/>
-    </row>
-    <row r="164" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A164" s="36"/>
-      <c r="B164" s="13"/>
-      <c r="C164" s="13"/>
-      <c r="D164" s="13"/>
-      <c r="E164" s="13"/>
-      <c r="F164" s="13"/>
-      <c r="G164" s="13"/>
-      <c r="H164" s="13"/>
-      <c r="I164" s="13"/>
-      <c r="J164" s="32"/>
-    </row>
-    <row r="165" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A165" s="6"/>
-      <c r="B165" s="3"/>
-      <c r="C165" s="3"/>
-      <c r="D165" s="3"/>
-      <c r="E165" s="3"/>
-      <c r="F165" s="3"/>
-      <c r="G165" s="3"/>
-      <c r="H165" s="3"/>
-      <c r="I165" s="3"/>
-      <c r="J165" s="8"/>
-    </row>
-    <row r="166" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A166" s="36"/>
-      <c r="B166" s="13"/>
-      <c r="C166" s="13"/>
-      <c r="D166" s="13"/>
-      <c r="E166" s="13"/>
-      <c r="F166" s="13"/>
-      <c r="G166" s="13"/>
-      <c r="H166" s="13"/>
-      <c r="I166" s="13"/>
-      <c r="J166" s="32"/>
-    </row>
-    <row r="167" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A167" s="6"/>
-      <c r="B167" s="3"/>
-      <c r="C167" s="3"/>
-      <c r="D167" s="3"/>
-      <c r="E167" s="3"/>
-      <c r="F167" s="3"/>
-      <c r="G167" s="3"/>
-      <c r="H167" s="3"/>
-      <c r="I167" s="3"/>
-      <c r="J167" s="8"/>
-    </row>
-    <row r="168" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A168" s="36"/>
-      <c r="B168" s="13"/>
-      <c r="C168" s="13"/>
-      <c r="D168" s="13"/>
-      <c r="E168" s="13"/>
-      <c r="F168" s="13"/>
-      <c r="G168" s="13"/>
-      <c r="H168" s="13"/>
-      <c r="I168" s="13"/>
-      <c r="J168" s="32"/>
-    </row>
-    <row r="169" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A169" s="6"/>
-      <c r="B169" s="3"/>
-      <c r="C169" s="3"/>
-      <c r="D169" s="3"/>
-      <c r="E169" s="3"/>
-      <c r="F169" s="3"/>
-      <c r="G169" s="3"/>
-      <c r="H169" s="3"/>
-      <c r="I169" s="3"/>
-      <c r="J169" s="8"/>
-    </row>
-    <row r="170" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A170" s="36"/>
-      <c r="B170" s="13"/>
-      <c r="C170" s="13"/>
-      <c r="D170" s="13"/>
-      <c r="E170" s="13"/>
-      <c r="F170" s="13"/>
-      <c r="G170" s="13"/>
-      <c r="H170" s="13"/>
-      <c r="I170" s="13"/>
-      <c r="J170" s="32"/>
-    </row>
-    <row r="171" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A171" s="6"/>
-      <c r="B171" s="3"/>
-      <c r="C171" s="3"/>
-      <c r="D171" s="3"/>
-      <c r="E171" s="3"/>
-      <c r="F171" s="3"/>
-      <c r="G171" s="3"/>
-      <c r="H171" s="3"/>
-      <c r="I171" s="3"/>
-      <c r="J171" s="8"/>
-    </row>
-    <row r="172" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A172" s="36"/>
-      <c r="B172" s="13"/>
-      <c r="C172" s="13"/>
-      <c r="D172" s="13"/>
-      <c r="E172" s="13"/>
-      <c r="F172" s="13"/>
-      <c r="G172" s="13"/>
-      <c r="H172" s="13"/>
-      <c r="I172" s="13"/>
-      <c r="J172" s="32"/>
-    </row>
-    <row r="173" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A173" s="6"/>
-      <c r="B173" s="3"/>
-      <c r="C173" s="3"/>
-      <c r="D173" s="3"/>
-      <c r="E173" s="3"/>
-      <c r="F173" s="3"/>
-      <c r="G173" s="3"/>
-      <c r="H173" s="3"/>
-      <c r="I173" s="3"/>
-      <c r="J173" s="8"/>
-    </row>
-    <row r="174" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A174" s="36"/>
-      <c r="B174" s="13"/>
-      <c r="C174" s="13"/>
-      <c r="D174" s="13"/>
-      <c r="E174" s="13"/>
-      <c r="F174" s="13"/>
-      <c r="G174" s="13"/>
-      <c r="H174" s="13"/>
-      <c r="I174" s="13"/>
-      <c r="J174" s="32"/>
-    </row>
-    <row r="175" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A175" s="6"/>
-      <c r="B175" s="3"/>
-      <c r="C175" s="3"/>
-      <c r="D175" s="3"/>
-      <c r="E175" s="3"/>
-      <c r="F175" s="3"/>
-      <c r="G175" s="3"/>
-      <c r="H175" s="3"/>
-      <c r="I175" s="3"/>
-      <c r="J175" s="8"/>
-    </row>
-    <row r="176" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A176" s="36"/>
-      <c r="B176" s="13"/>
-      <c r="C176" s="13"/>
-      <c r="D176" s="13"/>
-      <c r="E176" s="13"/>
-      <c r="F176" s="13"/>
-      <c r="G176" s="13"/>
-      <c r="H176" s="13"/>
-      <c r="I176" s="13"/>
-      <c r="J176" s="32"/>
-    </row>
-    <row r="177" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A177" s="6"/>
-      <c r="B177" s="3"/>
-      <c r="C177" s="3"/>
-      <c r="D177" s="3"/>
-      <c r="E177" s="3"/>
-      <c r="F177" s="3"/>
-      <c r="G177" s="3"/>
-      <c r="H177" s="3"/>
-      <c r="I177" s="3"/>
-      <c r="J177" s="8"/>
-    </row>
-    <row r="178" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A178" s="36"/>
-      <c r="B178" s="13"/>
-      <c r="C178" s="13"/>
-      <c r="D178" s="13"/>
-      <c r="E178" s="13"/>
-      <c r="F178" s="13"/>
-      <c r="G178" s="13"/>
-      <c r="H178" s="13"/>
-      <c r="I178" s="13"/>
-      <c r="J178" s="32"/>
-    </row>
-    <row r="179" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A179" s="6"/>
-      <c r="B179" s="3"/>
-      <c r="C179" s="3"/>
-      <c r="D179" s="3"/>
-      <c r="E179" s="3"/>
-      <c r="F179" s="3"/>
-      <c r="G179" s="3"/>
-      <c r="H179" s="3"/>
-      <c r="I179" s="3"/>
-      <c r="J179" s="8"/>
-    </row>
-    <row r="180" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A180" s="36"/>
-      <c r="B180" s="13"/>
-      <c r="C180" s="13"/>
-      <c r="D180" s="13"/>
-      <c r="E180" s="13"/>
-      <c r="F180" s="13"/>
-      <c r="G180" s="13"/>
-      <c r="H180" s="13"/>
-      <c r="I180" s="13"/>
-      <c r="J180" s="32"/>
-    </row>
-    <row r="181" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A181" s="6"/>
-      <c r="B181" s="3"/>
-      <c r="C181" s="3"/>
-      <c r="D181" s="3"/>
-      <c r="E181" s="3"/>
-      <c r="F181" s="3"/>
-      <c r="G181" s="3"/>
-      <c r="H181" s="3"/>
-      <c r="I181" s="3"/>
-      <c r="J181" s="8"/>
-    </row>
-    <row r="182" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A182" s="36"/>
-      <c r="B182" s="13"/>
-      <c r="C182" s="13"/>
-      <c r="D182" s="13"/>
-      <c r="E182" s="13"/>
-      <c r="F182" s="13"/>
-      <c r="G182" s="13"/>
-      <c r="H182" s="13"/>
-      <c r="I182" s="13"/>
-      <c r="J182" s="32"/>
-    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A160" s="9"/>
+      <c r="B160" s="10"/>
+      <c r="C160" s="10"/>
+      <c r="D160" s="10"/>
+      <c r="E160" s="10"/>
+      <c r="F160" s="10"/>
+      <c r="G160" s="10"/>
+      <c r="H160" s="10"/>
+      <c r="I160" s="10"/>
+      <c r="J160" s="11"/>
+    </row>
+    <row r="161" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="162" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="163" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="164" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="165" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="166" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <conditionalFormatting sqref="A1:B1 D1:J1">
+  <conditionalFormatting sqref="A1">
+    <cfRule type="expression" dxfId="5" priority="5">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A10:XFD1048576">
     <cfRule type="expression" dxfId="4" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A16:J182">
+  <conditionalFormatting sqref="B1 D1:J1">
     <cfRule type="expression" dxfId="3" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:G15">
+  <conditionalFormatting sqref="D5">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:J9 G10:G13 H10:J15">
+  <conditionalFormatting sqref="G2:XFD9">
     <cfRule type="expression" dxfId="1" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K1:XFD1">
+    <cfRule type="expression" dxfId="0" priority="6">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>